--- a/contratos.xlsx
+++ b/contratos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Downloads\UFPI\projetoPortarias\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Downloads\UFPI\projetoPortarias\site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B5228B-48EB-4F7B-BAFD-FED9F5DE5CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9899D0AA-4CB4-4F45-81FC-EB5CABEE2175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2009" sheetId="5" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9467" uniqueCount="1703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9823" uniqueCount="1703">
   <si>
     <t>PLANILHA REFERENTE AOS CONTRATOS DE 2009</t>
   </si>
@@ -6130,6 +6130,42 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6137,48 +6173,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6211,6 +6205,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6232,31 +6247,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6789,17 +6789,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="191" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="194"/>
-      <c r="C1" s="194"/>
-      <c r="D1" s="194"/>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
+      <c r="B1" s="192"/>
+      <c r="C1" s="192"/>
+      <c r="D1" s="192"/>
+      <c r="E1" s="192"/>
+      <c r="F1" s="192"/>
+      <c r="G1" s="192"/>
+      <c r="H1" s="192"/>
+      <c r="I1" s="192"/>
     </row>
     <row r="2" spans="1:9" ht="19.95" customHeight="1">
       <c r="A2" s="64" t="s">
@@ -6831,7 +6831,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="13.8" customHeight="1">
-      <c r="A3" s="195"/>
+      <c r="A3" s="193"/>
       <c r="B3" s="28" t="s">
         <v>10</v>
       </c>
@@ -6858,7 +6858,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="27.6">
-      <c r="A4" s="195"/>
+      <c r="A4" s="193"/>
       <c r="B4" s="28" t="s">
         <v>10</v>
       </c>
@@ -6885,7 +6885,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="27.6">
-      <c r="A5" s="195"/>
+      <c r="A5" s="193"/>
       <c r="B5" s="28" t="s">
         <v>10</v>
       </c>
@@ -7234,17 +7234,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="188" t="s">
         <v>957</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -16482,17 +16482,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="188" t="s">
         <v>1229</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -27151,17 +27151,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="188" t="s">
         <v>1504</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -27193,19 +27193,19 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1">
-      <c r="A3" s="179">
+      <c r="A3" s="153">
         <v>2016</v>
       </c>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="172" t="s">
         <v>1505</v>
       </c>
-      <c r="C3" s="179" t="s">
+      <c r="C3" s="153" t="s">
         <v>1506</v>
       </c>
-      <c r="D3" s="183" t="s">
+      <c r="D3" s="172" t="s">
         <v>1507</v>
       </c>
-      <c r="E3" s="189">
+      <c r="E3" s="171">
         <v>43250</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -27222,11 +27222,21 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
-      <c r="A4" s="179"/>
-      <c r="B4" s="183"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="183"/>
-      <c r="E4" s="189"/>
+      <c r="A4" s="153">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="172" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C4" s="153" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D4" s="172" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E4" s="171">
+        <v>43250</v>
+      </c>
       <c r="F4" s="8" t="s">
         <v>13</v>
       </c>
@@ -27241,11 +27251,21 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
-      <c r="A5" s="179"/>
-      <c r="B5" s="183"/>
-      <c r="C5" s="179"/>
-      <c r="D5" s="183"/>
-      <c r="E5" s="189"/>
+      <c r="A5" s="153">
+        <v>2016</v>
+      </c>
+      <c r="B5" s="172" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C5" s="153" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D5" s="172" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E5" s="171">
+        <v>43250</v>
+      </c>
       <c r="F5" s="8" t="s">
         <v>110</v>
       </c>
@@ -27260,13 +27280,19 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1">
-      <c r="A6" s="179"/>
-      <c r="B6" s="183"/>
-      <c r="C6" s="179"/>
-      <c r="D6" s="184" t="s">
+      <c r="A6" s="153">
+        <v>2016</v>
+      </c>
+      <c r="B6" s="172" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C6" s="153" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D6" s="167" t="s">
         <v>1508</v>
       </c>
-      <c r="E6" s="190">
+      <c r="E6" s="46">
         <v>43432</v>
       </c>
       <c r="F6" s="8" t="s">
@@ -27283,11 +27309,21 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1">
-      <c r="A7" s="179"/>
-      <c r="B7" s="183"/>
-      <c r="C7" s="179"/>
-      <c r="D7" s="184"/>
-      <c r="E7" s="190"/>
+      <c r="A7" s="153">
+        <v>2016</v>
+      </c>
+      <c r="B7" s="172" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C7" s="153" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D7" s="167" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E7" s="46">
+        <v>43432</v>
+      </c>
       <c r="F7" s="8" t="s">
         <v>13</v>
       </c>
@@ -27302,11 +27338,21 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
-      <c r="A8" s="179"/>
-      <c r="B8" s="183"/>
-      <c r="C8" s="179"/>
-      <c r="D8" s="184"/>
-      <c r="E8" s="190"/>
+      <c r="A8" s="153">
+        <v>2016</v>
+      </c>
+      <c r="B8" s="172" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C8" s="153" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D8" s="167" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E8" s="46">
+        <v>43432</v>
+      </c>
       <c r="F8" s="8" t="s">
         <v>110</v>
       </c>
@@ -27321,19 +27367,19 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
-      <c r="A9" s="180">
+      <c r="A9" s="176">
         <v>2017</v>
       </c>
-      <c r="B9" s="185" t="s">
+      <c r="B9" s="177" t="s">
         <v>1510</v>
       </c>
-      <c r="C9" s="180" t="s">
+      <c r="C9" s="176" t="s">
         <v>1511</v>
       </c>
-      <c r="D9" s="185" t="s">
+      <c r="D9" s="177" t="s">
         <v>1512</v>
       </c>
-      <c r="E9" s="191">
+      <c r="E9" s="178">
         <v>43599</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -27350,11 +27396,21 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
-      <c r="A10" s="179"/>
-      <c r="B10" s="183"/>
-      <c r="C10" s="179"/>
-      <c r="D10" s="183"/>
-      <c r="E10" s="189"/>
+      <c r="A10" s="176">
+        <v>2017</v>
+      </c>
+      <c r="B10" s="177" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C10" s="176" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D10" s="177" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E10" s="178">
+        <v>43599</v>
+      </c>
       <c r="F10" s="8" t="s">
         <v>13</v>
       </c>
@@ -27369,11 +27425,21 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
-      <c r="A11" s="181"/>
-      <c r="B11" s="186"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="186"/>
-      <c r="E11" s="192"/>
+      <c r="A11" s="176">
+        <v>2017</v>
+      </c>
+      <c r="B11" s="177" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C11" s="176" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D11" s="177" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E11" s="178">
+        <v>43599</v>
+      </c>
       <c r="F11" s="8" t="s">
         <v>110</v>
       </c>
@@ -27388,19 +27454,19 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
-      <c r="A12" s="180">
+      <c r="A12" s="176">
         <v>2018</v>
       </c>
-      <c r="B12" s="185" t="s">
+      <c r="B12" s="177" t="s">
         <v>1514</v>
       </c>
-      <c r="C12" s="180" t="s">
+      <c r="C12" s="176" t="s">
         <v>1515</v>
       </c>
-      <c r="D12" s="185" t="s">
+      <c r="D12" s="177" t="s">
         <v>1516</v>
       </c>
-      <c r="E12" s="191">
+      <c r="E12" s="178">
         <v>43621</v>
       </c>
       <c r="F12" s="8" t="s">
@@ -27417,11 +27483,21 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
-      <c r="A13" s="179"/>
-      <c r="B13" s="183"/>
-      <c r="C13" s="179"/>
-      <c r="D13" s="183"/>
-      <c r="E13" s="189"/>
+      <c r="A13" s="176">
+        <v>2018</v>
+      </c>
+      <c r="B13" s="177" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C13" s="176" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D13" s="177" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E13" s="178">
+        <v>43621</v>
+      </c>
       <c r="F13" s="8" t="s">
         <v>13</v>
       </c>
@@ -27436,11 +27512,21 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
-      <c r="A14" s="179"/>
-      <c r="B14" s="183"/>
-      <c r="C14" s="179"/>
-      <c r="D14" s="183"/>
-      <c r="E14" s="189"/>
+      <c r="A14" s="176">
+        <v>2018</v>
+      </c>
+      <c r="B14" s="177" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C14" s="176" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D14" s="177" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E14" s="178">
+        <v>43621</v>
+      </c>
       <c r="F14" s="8" t="s">
         <v>110</v>
       </c>
@@ -27455,19 +27541,19 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
-      <c r="A15" s="180">
+      <c r="A15" s="176">
         <v>2018</v>
       </c>
-      <c r="B15" s="185" t="s">
+      <c r="B15" s="177" t="s">
         <v>1155</v>
       </c>
-      <c r="C15" s="180" t="s">
+      <c r="C15" s="176" t="s">
         <v>1517</v>
       </c>
-      <c r="D15" s="185" t="s">
+      <c r="D15" s="177" t="s">
         <v>1518</v>
       </c>
-      <c r="E15" s="191">
+      <c r="E15" s="178">
         <v>43621</v>
       </c>
       <c r="F15" s="8" t="s">
@@ -27484,11 +27570,21 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
-      <c r="A16" s="179"/>
-      <c r="B16" s="183"/>
-      <c r="C16" s="179"/>
-      <c r="D16" s="183"/>
-      <c r="E16" s="189"/>
+      <c r="A16" s="176">
+        <v>2018</v>
+      </c>
+      <c r="B16" s="177" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C16" s="176" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D16" s="177" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E16" s="178">
+        <v>43621</v>
+      </c>
       <c r="F16" s="8" t="s">
         <v>13</v>
       </c>
@@ -27503,11 +27599,21 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="179"/>
-      <c r="B17" s="183"/>
-      <c r="C17" s="179"/>
-      <c r="D17" s="183"/>
-      <c r="E17" s="189"/>
+      <c r="A17" s="176">
+        <v>2018</v>
+      </c>
+      <c r="B17" s="177" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C17" s="176" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D17" s="177" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E17" s="178">
+        <v>43621</v>
+      </c>
       <c r="F17" s="8" t="s">
         <v>110</v>
       </c>
@@ -27522,19 +27628,19 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
-      <c r="A18" s="180">
+      <c r="A18" s="176">
         <v>2018</v>
       </c>
-      <c r="B18" s="185" t="s">
+      <c r="B18" s="177" t="s">
         <v>1519</v>
       </c>
-      <c r="C18" s="180" t="s">
+      <c r="C18" s="176" t="s">
         <v>1520</v>
       </c>
-      <c r="D18" s="185" t="s">
+      <c r="D18" s="177" t="s">
         <v>1521</v>
       </c>
-      <c r="E18" s="191">
+      <c r="E18" s="178">
         <v>43599</v>
       </c>
       <c r="F18" s="8" t="s">
@@ -27551,11 +27657,21 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1">
-      <c r="A19" s="179"/>
-      <c r="B19" s="183"/>
-      <c r="C19" s="179"/>
-      <c r="D19" s="183"/>
-      <c r="E19" s="189"/>
+      <c r="A19" s="176">
+        <v>2018</v>
+      </c>
+      <c r="B19" s="177" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C19" s="176" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D19" s="177" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E19" s="178">
+        <v>43599</v>
+      </c>
       <c r="F19" s="8" t="s">
         <v>13</v>
       </c>
@@ -27570,11 +27686,21 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1">
-      <c r="A20" s="181"/>
-      <c r="B20" s="186"/>
-      <c r="C20" s="181"/>
-      <c r="D20" s="186"/>
-      <c r="E20" s="192"/>
+      <c r="A20" s="176">
+        <v>2018</v>
+      </c>
+      <c r="B20" s="177" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C20" s="176" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D20" s="177" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E20" s="178">
+        <v>43599</v>
+      </c>
       <c r="F20" s="8" t="s">
         <v>110</v>
       </c>
@@ -27589,19 +27715,19 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1">
-      <c r="A21" s="180">
+      <c r="A21" s="176">
         <v>2019</v>
       </c>
-      <c r="B21" s="185" t="s">
+      <c r="B21" s="177" t="s">
         <v>1522</v>
       </c>
-      <c r="C21" s="180" t="s">
+      <c r="C21" s="176" t="s">
         <v>1523</v>
       </c>
-      <c r="D21" s="185" t="s">
+      <c r="D21" s="177" t="s">
         <v>1524</v>
       </c>
-      <c r="E21" s="191">
+      <c r="E21" s="178">
         <v>43612</v>
       </c>
       <c r="F21" s="16" t="s">
@@ -27618,11 +27744,21 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1">
-      <c r="A22" s="179"/>
-      <c r="B22" s="183"/>
-      <c r="C22" s="179"/>
-      <c r="D22" s="183"/>
-      <c r="E22" s="189"/>
+      <c r="A22" s="176">
+        <v>2019</v>
+      </c>
+      <c r="B22" s="177" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C22" s="176" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D22" s="177" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E22" s="178">
+        <v>43612</v>
+      </c>
       <c r="F22" s="16" t="s">
         <v>13</v>
       </c>
@@ -27637,11 +27773,21 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1">
-      <c r="A23" s="181"/>
-      <c r="B23" s="186"/>
-      <c r="C23" s="181"/>
-      <c r="D23" s="186"/>
-      <c r="E23" s="192"/>
+      <c r="A23" s="176">
+        <v>2019</v>
+      </c>
+      <c r="B23" s="177" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C23" s="176" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D23" s="177" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E23" s="178">
+        <v>43612</v>
+      </c>
       <c r="F23" s="16" t="s">
         <v>110</v>
       </c>
@@ -27656,19 +27802,19 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1">
-      <c r="A24" s="182">
+      <c r="A24" s="183">
         <v>2019</v>
       </c>
       <c r="B24" s="184" t="s">
         <v>1527</v>
       </c>
-      <c r="C24" s="182" t="s">
+      <c r="C24" s="183" t="s">
         <v>1528</v>
       </c>
       <c r="D24" s="184" t="s">
         <v>1529</v>
       </c>
-      <c r="E24" s="190">
+      <c r="E24" s="185">
         <v>43802</v>
       </c>
       <c r="F24" s="16" t="s">
@@ -27685,11 +27831,21 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1">
-      <c r="A25" s="182"/>
-      <c r="B25" s="184"/>
-      <c r="C25" s="182"/>
-      <c r="D25" s="184"/>
-      <c r="E25" s="190"/>
+      <c r="A25" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B25" s="184" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C25" s="183" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D25" s="184" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E25" s="185">
+        <v>43802</v>
+      </c>
       <c r="F25" s="16" t="s">
         <v>13</v>
       </c>
@@ -27704,11 +27860,21 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1">
-      <c r="A26" s="182"/>
-      <c r="B26" s="184"/>
-      <c r="C26" s="182"/>
-      <c r="D26" s="184"/>
-      <c r="E26" s="190"/>
+      <c r="A26" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B26" s="184" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C26" s="183" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D26" s="184" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E26" s="185">
+        <v>43802</v>
+      </c>
       <c r="F26" s="16" t="s">
         <v>110</v>
       </c>
@@ -27723,19 +27889,19 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1">
-      <c r="A27" s="182">
+      <c r="A27" s="183">
         <v>2019</v>
       </c>
       <c r="B27" s="184" t="s">
         <v>1533</v>
       </c>
-      <c r="C27" s="182" t="s">
+      <c r="C27" s="183" t="s">
         <v>1534</v>
       </c>
       <c r="D27" s="184" t="s">
         <v>1535</v>
       </c>
-      <c r="E27" s="190">
+      <c r="E27" s="185">
         <v>43802</v>
       </c>
       <c r="F27" s="16" t="s">
@@ -27752,11 +27918,21 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1">
-      <c r="A28" s="182"/>
-      <c r="B28" s="184"/>
-      <c r="C28" s="182"/>
-      <c r="D28" s="184"/>
-      <c r="E28" s="190"/>
+      <c r="A28" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B28" s="184" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C28" s="183" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D28" s="184" t="s">
+        <v>1535</v>
+      </c>
+      <c r="E28" s="185">
+        <v>43802</v>
+      </c>
       <c r="F28" s="16" t="s">
         <v>13</v>
       </c>
@@ -27771,11 +27947,21 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1">
-      <c r="A29" s="182"/>
-      <c r="B29" s="184"/>
-      <c r="C29" s="182"/>
-      <c r="D29" s="184"/>
-      <c r="E29" s="190"/>
+      <c r="A29" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B29" s="184" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C29" s="183" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D29" s="184" t="s">
+        <v>1535</v>
+      </c>
+      <c r="E29" s="185">
+        <v>43802</v>
+      </c>
       <c r="F29" s="16" t="s">
         <v>110</v>
       </c>
@@ -27790,19 +27976,19 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1">
-      <c r="A30" s="182">
+      <c r="A30" s="183">
         <v>2019</v>
       </c>
       <c r="B30" s="184" t="s">
         <v>1230</v>
       </c>
-      <c r="C30" s="182" t="s">
+      <c r="C30" s="183" t="s">
         <v>1536</v>
       </c>
       <c r="D30" s="184" t="s">
         <v>1537</v>
       </c>
-      <c r="E30" s="190">
+      <c r="E30" s="185">
         <v>43802</v>
       </c>
       <c r="F30" s="16" t="s">
@@ -27819,11 +28005,21 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1">
-      <c r="A31" s="182"/>
-      <c r="B31" s="184"/>
-      <c r="C31" s="182"/>
-      <c r="D31" s="184"/>
-      <c r="E31" s="190"/>
+      <c r="A31" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B31" s="184" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C31" s="183" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D31" s="184" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E31" s="185">
+        <v>43802</v>
+      </c>
       <c r="F31" s="16" t="s">
         <v>13</v>
       </c>
@@ -27838,11 +28034,21 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1">
-      <c r="A32" s="182"/>
-      <c r="B32" s="184"/>
-      <c r="C32" s="182"/>
-      <c r="D32" s="184"/>
-      <c r="E32" s="190"/>
+      <c r="A32" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B32" s="184" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C32" s="183" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D32" s="184" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E32" s="185">
+        <v>43802</v>
+      </c>
       <c r="F32" s="16" t="s">
         <v>110</v>
       </c>
@@ -27857,19 +28063,19 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15" customHeight="1">
-      <c r="A33" s="180">
+      <c r="A33" s="176">
         <v>2019</v>
       </c>
-      <c r="B33" s="185" t="s">
+      <c r="B33" s="177" t="s">
         <v>1206</v>
       </c>
-      <c r="C33" s="180" t="s">
+      <c r="C33" s="176" t="s">
         <v>1538</v>
       </c>
-      <c r="D33" s="185" t="s">
+      <c r="D33" s="177" t="s">
         <v>1539</v>
       </c>
-      <c r="E33" s="191">
+      <c r="E33" s="178">
         <v>43663</v>
       </c>
       <c r="F33" s="16" t="s">
@@ -27886,11 +28092,21 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1">
-      <c r="A34" s="179"/>
-      <c r="B34" s="183"/>
-      <c r="C34" s="179"/>
-      <c r="D34" s="183"/>
-      <c r="E34" s="189"/>
+      <c r="A34" s="176">
+        <v>2019</v>
+      </c>
+      <c r="B34" s="177" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C34" s="176" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D34" s="177" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E34" s="178">
+        <v>43663</v>
+      </c>
       <c r="F34" s="16" t="s">
         <v>13</v>
       </c>
@@ -27905,11 +28121,21 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1">
-      <c r="A35" s="181"/>
-      <c r="B35" s="186"/>
-      <c r="C35" s="181"/>
-      <c r="D35" s="186"/>
-      <c r="E35" s="192"/>
+      <c r="A35" s="176">
+        <v>2019</v>
+      </c>
+      <c r="B35" s="177" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C35" s="176" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D35" s="177" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E35" s="178">
+        <v>43663</v>
+      </c>
       <c r="F35" s="16" t="s">
         <v>110</v>
       </c>
@@ -27924,19 +28150,19 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" customHeight="1">
-      <c r="A36" s="182">
+      <c r="A36" s="183">
         <v>2019</v>
       </c>
       <c r="B36" s="184" t="s">
         <v>1210</v>
       </c>
-      <c r="C36" s="182" t="s">
+      <c r="C36" s="183" t="s">
         <v>1543</v>
       </c>
       <c r="D36" s="184" t="s">
         <v>1544</v>
       </c>
-      <c r="E36" s="190">
+      <c r="E36" s="185">
         <v>43802</v>
       </c>
       <c r="F36" s="16" t="s">
@@ -27953,11 +28179,21 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1">
-      <c r="A37" s="182"/>
-      <c r="B37" s="184"/>
-      <c r="C37" s="182"/>
-      <c r="D37" s="184"/>
-      <c r="E37" s="190"/>
+      <c r="A37" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B37" s="184" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C37" s="183" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D37" s="184" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E37" s="185">
+        <v>43802</v>
+      </c>
       <c r="F37" s="16" t="s">
         <v>13</v>
       </c>
@@ -27972,11 +28208,21 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1">
-      <c r="A38" s="182"/>
-      <c r="B38" s="184"/>
-      <c r="C38" s="182"/>
-      <c r="D38" s="184"/>
-      <c r="E38" s="190"/>
+      <c r="A38" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B38" s="184" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C38" s="183" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D38" s="184" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E38" s="185">
+        <v>43802</v>
+      </c>
       <c r="F38" s="16" t="s">
         <v>110</v>
       </c>
@@ -27991,19 +28237,19 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1">
-      <c r="A39" s="182">
+      <c r="A39" s="183">
         <v>2019</v>
       </c>
       <c r="B39" s="184" t="s">
         <v>1224</v>
       </c>
-      <c r="C39" s="182" t="s">
+      <c r="C39" s="183" t="s">
         <v>1548</v>
       </c>
       <c r="D39" s="184" t="s">
         <v>1549</v>
       </c>
-      <c r="E39" s="190">
+      <c r="E39" s="185">
         <v>43803</v>
       </c>
       <c r="F39" s="16" t="s">
@@ -28020,11 +28266,21 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1">
-      <c r="A40" s="182"/>
-      <c r="B40" s="184"/>
-      <c r="C40" s="182"/>
-      <c r="D40" s="184"/>
-      <c r="E40" s="190"/>
+      <c r="A40" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B40" s="184" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C40" s="183" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D40" s="184" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E40" s="185">
+        <v>43803</v>
+      </c>
       <c r="F40" s="16" t="s">
         <v>13</v>
       </c>
@@ -28039,11 +28295,21 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="15" customHeight="1">
-      <c r="A41" s="182"/>
-      <c r="B41" s="184"/>
-      <c r="C41" s="182"/>
-      <c r="D41" s="184"/>
-      <c r="E41" s="190"/>
+      <c r="A41" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B41" s="184" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C41" s="183" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D41" s="184" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E41" s="185">
+        <v>43803</v>
+      </c>
       <c r="F41" s="16" t="s">
         <v>110</v>
       </c>
@@ -28058,19 +28324,19 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1">
-      <c r="A42" s="180">
+      <c r="A42" s="176">
         <v>2019</v>
       </c>
-      <c r="B42" s="185" t="s">
+      <c r="B42" s="177" t="s">
         <v>1240</v>
       </c>
-      <c r="C42" s="180" t="s">
+      <c r="C42" s="176" t="s">
         <v>1554</v>
       </c>
-      <c r="D42" s="185" t="s">
+      <c r="D42" s="177" t="s">
         <v>1555</v>
       </c>
-      <c r="E42" s="191">
+      <c r="E42" s="178">
         <v>43812</v>
       </c>
       <c r="F42" s="16" t="s">
@@ -28087,11 +28353,21 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1">
-      <c r="A43" s="179"/>
-      <c r="B43" s="183"/>
-      <c r="C43" s="179"/>
-      <c r="D43" s="183"/>
-      <c r="E43" s="189"/>
+      <c r="A43" s="176">
+        <v>2019</v>
+      </c>
+      <c r="B43" s="177" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C43" s="176" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D43" s="177" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E43" s="178">
+        <v>43812</v>
+      </c>
       <c r="F43" s="16" t="s">
         <v>13</v>
       </c>
@@ -28106,11 +28382,21 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1">
-      <c r="A44" s="181"/>
-      <c r="B44" s="186"/>
-      <c r="C44" s="181"/>
-      <c r="D44" s="186"/>
-      <c r="E44" s="192"/>
+      <c r="A44" s="176">
+        <v>2019</v>
+      </c>
+      <c r="B44" s="177" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C44" s="176" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D44" s="177" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E44" s="178">
+        <v>43812</v>
+      </c>
       <c r="F44" s="16" t="s">
         <v>110</v>
       </c>
@@ -28125,19 +28411,19 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" customHeight="1">
-      <c r="A45" s="182">
+      <c r="A45" s="183">
         <v>2019</v>
       </c>
       <c r="B45" s="184" t="s">
         <v>1232</v>
       </c>
-      <c r="C45" s="182" t="s">
+      <c r="C45" s="183" t="s">
         <v>1556</v>
       </c>
       <c r="D45" s="184" t="s">
         <v>1557</v>
       </c>
-      <c r="E45" s="190">
+      <c r="E45" s="185">
         <v>43802</v>
       </c>
       <c r="F45" s="16" t="s">
@@ -28154,11 +28440,21 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" customHeight="1">
-      <c r="A46" s="182"/>
-      <c r="B46" s="184"/>
-      <c r="C46" s="182"/>
-      <c r="D46" s="184"/>
-      <c r="E46" s="190"/>
+      <c r="A46" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B46" s="184" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C46" s="183" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D46" s="184" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E46" s="185">
+        <v>43802</v>
+      </c>
       <c r="F46" s="16" t="s">
         <v>13</v>
       </c>
@@ -28173,11 +28469,21 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1">
-      <c r="A47" s="182"/>
-      <c r="B47" s="184"/>
-      <c r="C47" s="182"/>
-      <c r="D47" s="184"/>
-      <c r="E47" s="190"/>
+      <c r="A47" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B47" s="184" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C47" s="183" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D47" s="184" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E47" s="185">
+        <v>43802</v>
+      </c>
       <c r="F47" s="16" t="s">
         <v>110</v>
       </c>
@@ -28192,19 +28498,19 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="15" customHeight="1">
-      <c r="A48" s="182">
+      <c r="A48" s="183">
         <v>2019</v>
       </c>
       <c r="B48" s="184" t="s">
         <v>1246</v>
       </c>
-      <c r="C48" s="182" t="s">
+      <c r="C48" s="183" t="s">
         <v>1560</v>
       </c>
       <c r="D48" s="184" t="s">
         <v>1561</v>
       </c>
-      <c r="E48" s="190">
+      <c r="E48" s="185">
         <v>43802</v>
       </c>
       <c r="F48" s="16" t="s">
@@ -28221,11 +28527,21 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1">
-      <c r="A49" s="182"/>
-      <c r="B49" s="184"/>
-      <c r="C49" s="182"/>
-      <c r="D49" s="184"/>
-      <c r="E49" s="190"/>
+      <c r="A49" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B49" s="184" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C49" s="183" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D49" s="184" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E49" s="185">
+        <v>43802</v>
+      </c>
       <c r="F49" s="16" t="s">
         <v>13</v>
       </c>
@@ -28240,11 +28556,21 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1">
-      <c r="A50" s="182"/>
-      <c r="B50" s="184"/>
-      <c r="C50" s="182"/>
-      <c r="D50" s="184"/>
-      <c r="E50" s="190"/>
+      <c r="A50" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B50" s="184" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C50" s="183" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D50" s="184" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E50" s="185">
+        <v>43802</v>
+      </c>
       <c r="F50" s="16" t="s">
         <v>110</v>
       </c>
@@ -28259,19 +28585,19 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1">
-      <c r="A51" s="182">
+      <c r="A51" s="183">
         <v>2019</v>
       </c>
       <c r="B51" s="184" t="s">
         <v>1272</v>
       </c>
-      <c r="C51" s="182" t="s">
+      <c r="C51" s="183" t="s">
         <v>1562</v>
       </c>
       <c r="D51" s="184" t="s">
         <v>1563</v>
       </c>
-      <c r="E51" s="190">
+      <c r="E51" s="185">
         <v>43803</v>
       </c>
       <c r="F51" s="16" t="s">
@@ -28288,11 +28614,21 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1">
-      <c r="A52" s="182"/>
-      <c r="B52" s="184"/>
-      <c r="C52" s="182"/>
-      <c r="D52" s="184"/>
-      <c r="E52" s="190"/>
+      <c r="A52" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B52" s="184" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C52" s="183" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D52" s="184" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E52" s="185">
+        <v>43803</v>
+      </c>
       <c r="F52" s="16" t="s">
         <v>13</v>
       </c>
@@ -28307,11 +28643,21 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1">
-      <c r="A53" s="182"/>
-      <c r="B53" s="184"/>
-      <c r="C53" s="182"/>
-      <c r="D53" s="184"/>
-      <c r="E53" s="190"/>
+      <c r="A53" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B53" s="184" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C53" s="183" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D53" s="184" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E53" s="185">
+        <v>43803</v>
+      </c>
       <c r="F53" s="16" t="s">
         <v>110</v>
       </c>
@@ -28329,16 +28675,16 @@
       <c r="A54" s="179">
         <v>2019</v>
       </c>
-      <c r="B54" s="183" t="s">
+      <c r="B54" s="180" t="s">
         <v>1275</v>
       </c>
       <c r="C54" s="179" t="s">
         <v>877</v>
       </c>
-      <c r="D54" s="183" t="s">
+      <c r="D54" s="180" t="s">
         <v>1568</v>
       </c>
-      <c r="E54" s="189">
+      <c r="E54" s="181">
         <v>43719</v>
       </c>
       <c r="F54" s="16" t="s">
@@ -28355,11 +28701,21 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1">
-      <c r="A55" s="179"/>
-      <c r="B55" s="183"/>
-      <c r="C55" s="179"/>
-      <c r="D55" s="183"/>
-      <c r="E55" s="189"/>
+      <c r="A55" s="179">
+        <v>2019</v>
+      </c>
+      <c r="B55" s="180" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C55" s="179" t="s">
+        <v>877</v>
+      </c>
+      <c r="D55" s="180" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E55" s="181">
+        <v>43719</v>
+      </c>
       <c r="F55" s="16" t="s">
         <v>879</v>
       </c>
@@ -28374,11 +28730,21 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1">
-      <c r="A56" s="179"/>
-      <c r="B56" s="183"/>
-      <c r="C56" s="179"/>
-      <c r="D56" s="183"/>
-      <c r="E56" s="189"/>
+      <c r="A56" s="179">
+        <v>2019</v>
+      </c>
+      <c r="B56" s="180" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C56" s="179" t="s">
+        <v>877</v>
+      </c>
+      <c r="D56" s="180" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E56" s="181">
+        <v>43719</v>
+      </c>
       <c r="F56" s="16" t="s">
         <v>13</v>
       </c>
@@ -28393,11 +28759,21 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1">
-      <c r="A57" s="179"/>
-      <c r="B57" s="183"/>
-      <c r="C57" s="179"/>
-      <c r="D57" s="183"/>
-      <c r="E57" s="189"/>
+      <c r="A57" s="179">
+        <v>2019</v>
+      </c>
+      <c r="B57" s="180" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C57" s="179" t="s">
+        <v>877</v>
+      </c>
+      <c r="D57" s="180" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E57" s="181">
+        <v>43719</v>
+      </c>
       <c r="F57" s="16" t="s">
         <v>110</v>
       </c>
@@ -28412,19 +28788,19 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1">
-      <c r="A58" s="182">
+      <c r="A58" s="183">
         <v>2019</v>
       </c>
       <c r="B58" s="184" t="s">
         <v>1280</v>
       </c>
-      <c r="C58" s="182" t="s">
+      <c r="C58" s="183" t="s">
         <v>1569</v>
       </c>
       <c r="D58" s="184" t="s">
         <v>1570</v>
       </c>
-      <c r="E58" s="190">
+      <c r="E58" s="185">
         <v>43760</v>
       </c>
       <c r="F58" s="16" t="s">
@@ -28441,11 +28817,21 @@
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1">
-      <c r="A59" s="182"/>
-      <c r="B59" s="184"/>
-      <c r="C59" s="182"/>
-      <c r="D59" s="184"/>
-      <c r="E59" s="190"/>
+      <c r="A59" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B59" s="184" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C59" s="183" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D59" s="184" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E59" s="185">
+        <v>43760</v>
+      </c>
       <c r="F59" s="16" t="s">
         <v>13</v>
       </c>
@@ -28460,11 +28846,21 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1">
-      <c r="A60" s="182"/>
-      <c r="B60" s="184"/>
-      <c r="C60" s="182"/>
-      <c r="D60" s="184"/>
-      <c r="E60" s="190"/>
+      <c r="A60" s="183">
+        <v>2019</v>
+      </c>
+      <c r="B60" s="184" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C60" s="183" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D60" s="184" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E60" s="185">
+        <v>43760</v>
+      </c>
       <c r="F60" s="16" t="s">
         <v>110</v>
       </c>
@@ -28479,19 +28875,19 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1">
-      <c r="A61" s="180">
+      <c r="A61" s="176">
         <v>2020</v>
       </c>
-      <c r="B61" s="185" t="s">
+      <c r="B61" s="177" t="s">
         <v>1394</v>
       </c>
-      <c r="C61" s="180" t="s">
+      <c r="C61" s="176" t="s">
         <v>1090</v>
       </c>
-      <c r="D61" s="185" t="s">
+      <c r="D61" s="177" t="s">
         <v>1447</v>
       </c>
-      <c r="E61" s="191">
+      <c r="E61" s="178">
         <v>43868</v>
       </c>
       <c r="F61" s="16" t="s">
@@ -28508,11 +28904,21 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1">
-      <c r="A62" s="179"/>
-      <c r="B62" s="183"/>
-      <c r="C62" s="179"/>
-      <c r="D62" s="183"/>
-      <c r="E62" s="179"/>
+      <c r="A62" s="176">
+        <v>2020</v>
+      </c>
+      <c r="B62" s="177" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C62" s="176" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D62" s="177" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E62" s="178">
+        <v>43868</v>
+      </c>
       <c r="F62" s="16" t="s">
         <v>13</v>
       </c>
@@ -28527,11 +28933,21 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1">
-      <c r="A63" s="179"/>
-      <c r="B63" s="183"/>
-      <c r="C63" s="179"/>
-      <c r="D63" s="183"/>
-      <c r="E63" s="179"/>
+      <c r="A63" s="176">
+        <v>2020</v>
+      </c>
+      <c r="B63" s="177" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C63" s="176" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D63" s="177" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E63" s="178">
+        <v>43868</v>
+      </c>
       <c r="F63" s="16" t="s">
         <v>110</v>
       </c>
@@ -28546,19 +28962,19 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1">
-      <c r="A64" s="180">
+      <c r="A64" s="176">
         <v>2020</v>
       </c>
-      <c r="B64" s="185" t="s">
+      <c r="B64" s="177" t="s">
         <v>1397</v>
       </c>
-      <c r="C64" s="180" t="s">
+      <c r="C64" s="176" t="s">
         <v>1576</v>
       </c>
-      <c r="D64" s="185" t="s">
+      <c r="D64" s="177" t="s">
         <v>1438</v>
       </c>
-      <c r="E64" s="191">
+      <c r="E64" s="178">
         <v>43864</v>
       </c>
       <c r="F64" s="16" t="s">
@@ -28575,11 +28991,21 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="15" customHeight="1">
-      <c r="A65" s="179"/>
-      <c r="B65" s="183"/>
-      <c r="C65" s="179"/>
-      <c r="D65" s="183"/>
-      <c r="E65" s="189"/>
+      <c r="A65" s="176">
+        <v>2020</v>
+      </c>
+      <c r="B65" s="177" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C65" s="176" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D65" s="177" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E65" s="178">
+        <v>43864</v>
+      </c>
       <c r="F65" s="16" t="s">
         <v>13</v>
       </c>
@@ -28594,11 +29020,21 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="15" customHeight="1">
-      <c r="A66" s="181"/>
-      <c r="B66" s="186"/>
-      <c r="C66" s="181"/>
-      <c r="D66" s="186"/>
-      <c r="E66" s="192"/>
+      <c r="A66" s="176">
+        <v>2020</v>
+      </c>
+      <c r="B66" s="177" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C66" s="176" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D66" s="177" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E66" s="178">
+        <v>43864</v>
+      </c>
       <c r="F66" s="16" t="s">
         <v>110</v>
       </c>
@@ -28613,17 +29049,17 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="15" customHeight="1">
-      <c r="A67" s="180"/>
-      <c r="B67" s="185" t="s">
+      <c r="A67" s="176"/>
+      <c r="B67" s="177" t="s">
         <v>1216</v>
       </c>
-      <c r="C67" s="180" t="s">
+      <c r="C67" s="176" t="s">
         <v>1577</v>
       </c>
-      <c r="D67" s="185" t="s">
+      <c r="D67" s="177" t="s">
         <v>1578</v>
       </c>
-      <c r="E67" s="191">
+      <c r="E67" s="178">
         <v>43879</v>
       </c>
       <c r="F67" s="16" t="s">
@@ -28641,10 +29077,18 @@
     </row>
     <row r="68" spans="1:9" ht="15" customHeight="1">
       <c r="A68" s="179"/>
-      <c r="B68" s="183"/>
-      <c r="C68" s="179"/>
-      <c r="D68" s="183"/>
-      <c r="E68" s="179"/>
+      <c r="B68" s="177" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C68" s="176" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D68" s="177" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E68" s="178">
+        <v>43879</v>
+      </c>
       <c r="F68" s="16" t="s">
         <v>13</v>
       </c>
@@ -28659,11 +29103,19 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="15" customHeight="1">
-      <c r="A69" s="181"/>
-      <c r="B69" s="186"/>
-      <c r="C69" s="181"/>
-      <c r="D69" s="186"/>
-      <c r="E69" s="181"/>
+      <c r="A69" s="182"/>
+      <c r="B69" s="177" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C69" s="176" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D69" s="177" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E69" s="178">
+        <v>43879</v>
+      </c>
       <c r="F69" s="16" t="s">
         <v>110</v>
       </c>
@@ -28678,17 +29130,17 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1">
-      <c r="A70" s="16"/>
-      <c r="B70" s="185" t="s">
+      <c r="A70" s="186"/>
+      <c r="B70" s="177" t="s">
         <v>1412</v>
       </c>
-      <c r="C70" s="180" t="s">
+      <c r="C70" s="176" t="s">
         <v>1579</v>
       </c>
-      <c r="D70" s="185" t="s">
+      <c r="D70" s="177" t="s">
         <v>1580</v>
       </c>
-      <c r="E70" s="191">
+      <c r="E70" s="178">
         <v>43879</v>
       </c>
       <c r="F70" s="16" t="s">
@@ -28705,11 +29157,19 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1">
-      <c r="A71" s="16"/>
-      <c r="B71" s="183"/>
-      <c r="C71" s="187"/>
-      <c r="D71" s="183"/>
-      <c r="E71" s="179"/>
+      <c r="A71" s="186"/>
+      <c r="B71" s="177" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C71" s="176" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D71" s="177" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E71" s="178">
+        <v>43879</v>
+      </c>
       <c r="F71" s="16" t="s">
         <v>13</v>
       </c>
@@ -28724,11 +29184,19 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1">
-      <c r="A72" s="16"/>
-      <c r="B72" s="186"/>
-      <c r="C72" s="188"/>
-      <c r="D72" s="186"/>
-      <c r="E72" s="181"/>
+      <c r="A72" s="186"/>
+      <c r="B72" s="177" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C72" s="176" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D72" s="177" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E72" s="178">
+        <v>43879</v>
+      </c>
       <c r="F72" s="16" t="s">
         <v>110</v>
       </c>
@@ -28743,17 +29211,17 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1">
-      <c r="A73" s="16"/>
-      <c r="B73" s="185" t="s">
+      <c r="A73" s="186"/>
+      <c r="B73" s="177" t="s">
         <v>1581</v>
       </c>
-      <c r="C73" s="180" t="s">
+      <c r="C73" s="176" t="s">
         <v>1582</v>
       </c>
-      <c r="D73" s="185" t="s">
+      <c r="D73" s="177" t="s">
         <v>1583</v>
       </c>
-      <c r="E73" s="191">
+      <c r="E73" s="178">
         <v>43879</v>
       </c>
       <c r="F73" s="16" t="s">
@@ -28770,11 +29238,19 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1">
-      <c r="A74" s="16"/>
-      <c r="B74" s="183"/>
-      <c r="C74" s="179"/>
-      <c r="D74" s="183"/>
-      <c r="E74" s="179"/>
+      <c r="A74" s="186"/>
+      <c r="B74" s="177" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C74" s="176" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D74" s="177" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E74" s="178">
+        <v>43879</v>
+      </c>
       <c r="F74" s="16" t="s">
         <v>13</v>
       </c>
@@ -28789,11 +29265,19 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1">
-      <c r="A75" s="16"/>
-      <c r="B75" s="183"/>
-      <c r="C75" s="179"/>
-      <c r="D75" s="186"/>
-      <c r="E75" s="181"/>
+      <c r="A75" s="186"/>
+      <c r="B75" s="177" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C75" s="176" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D75" s="177" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E75" s="178">
+        <v>43879</v>
+      </c>
       <c r="F75" s="16" t="s">
         <v>110</v>
       </c>
@@ -28808,12 +29292,17 @@
       </c>
     </row>
     <row r="76" spans="1:9">
-      <c r="B76" s="183"/>
-      <c r="C76" s="179"/>
-      <c r="D76" s="183" t="s">
+      <c r="A76" s="187"/>
+      <c r="B76" s="177" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C76" s="176" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D76" s="180" t="s">
         <v>1584</v>
       </c>
-      <c r="E76" s="189">
+      <c r="E76" s="181">
         <v>44160</v>
       </c>
       <c r="F76" s="16" t="s">
@@ -28830,10 +29319,19 @@
       </c>
     </row>
     <row r="77" spans="1:9">
-      <c r="B77" s="183"/>
-      <c r="C77" s="179"/>
-      <c r="D77" s="183"/>
-      <c r="E77" s="189"/>
+      <c r="A77" s="187"/>
+      <c r="B77" s="177" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C77" s="176" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D77" s="180" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E77" s="181">
+        <v>44160</v>
+      </c>
       <c r="F77" s="16" t="s">
         <v>13</v>
       </c>
@@ -28848,10 +29346,19 @@
       </c>
     </row>
     <row r="78" spans="1:9">
-      <c r="B78" s="186"/>
-      <c r="C78" s="181"/>
-      <c r="D78" s="183"/>
-      <c r="E78" s="189"/>
+      <c r="A78" s="187"/>
+      <c r="B78" s="177" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C78" s="176" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D78" s="180" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E78" s="181">
+        <v>44160</v>
+      </c>
       <c r="F78" s="16" t="s">
         <v>110</v>
       </c>
@@ -28866,16 +29373,17 @@
       </c>
     </row>
     <row r="79" spans="1:9">
+      <c r="A79" s="187"/>
       <c r="B79" s="184" t="s">
         <v>1402</v>
       </c>
-      <c r="C79" s="182" t="s">
+      <c r="C79" s="183" t="s">
         <v>1585</v>
       </c>
-      <c r="D79" s="185" t="s">
+      <c r="D79" s="177" t="s">
         <v>1463</v>
       </c>
-      <c r="E79" s="191">
+      <c r="E79" s="178">
         <v>43879</v>
       </c>
       <c r="F79" s="16" t="s">
@@ -28892,10 +29400,19 @@
       </c>
     </row>
     <row r="80" spans="1:9">
-      <c r="B80" s="184"/>
-      <c r="C80" s="182"/>
-      <c r="D80" s="183"/>
-      <c r="E80" s="179"/>
+      <c r="A80" s="187"/>
+      <c r="B80" s="184" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C80" s="183" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D80" s="177" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E80" s="178">
+        <v>43879</v>
+      </c>
       <c r="F80" s="16" t="s">
         <v>13</v>
       </c>
@@ -28909,11 +29426,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="2:9">
-      <c r="B81" s="184"/>
-      <c r="C81" s="182"/>
-      <c r="D81" s="186"/>
-      <c r="E81" s="181"/>
+    <row r="81" spans="1:9">
+      <c r="A81" s="187"/>
+      <c r="B81" s="184" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C81" s="183" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D81" s="177" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E81" s="178">
+        <v>43879</v>
+      </c>
       <c r="F81" s="16" t="s">
         <v>110</v>
       </c>
@@ -28927,17 +29453,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="2:9">
+    <row r="82" spans="1:9">
+      <c r="A82" s="187"/>
       <c r="B82" s="184" t="s">
         <v>1406</v>
       </c>
-      <c r="C82" s="182" t="s">
+      <c r="C82" s="183" t="s">
         <v>1586</v>
       </c>
-      <c r="D82" s="185" t="s">
+      <c r="D82" s="177" t="s">
         <v>1466</v>
       </c>
-      <c r="E82" s="191">
+      <c r="E82" s="178">
         <v>43879</v>
       </c>
       <c r="F82" s="16" t="s">
@@ -28953,11 +29480,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="2:9">
-      <c r="B83" s="184"/>
-      <c r="C83" s="182"/>
-      <c r="D83" s="183"/>
-      <c r="E83" s="179"/>
+    <row r="83" spans="1:9">
+      <c r="A83" s="187"/>
+      <c r="B83" s="184" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C83" s="183" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D83" s="177" t="s">
+        <v>1466</v>
+      </c>
+      <c r="E83" s="178">
+        <v>43879</v>
+      </c>
       <c r="F83" s="16" t="s">
         <v>13</v>
       </c>
@@ -28971,11 +29507,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="2:9">
-      <c r="B84" s="184"/>
-      <c r="C84" s="182"/>
-      <c r="D84" s="186"/>
-      <c r="E84" s="181"/>
+    <row r="84" spans="1:9">
+      <c r="A84" s="187"/>
+      <c r="B84" s="184" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C84" s="183" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D84" s="177" t="s">
+        <v>1466</v>
+      </c>
+      <c r="E84" s="178">
+        <v>43879</v>
+      </c>
       <c r="F84" s="16" t="s">
         <v>110</v>
       </c>
@@ -28989,17 +29534,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="2:9">
+    <row r="85" spans="1:9">
+      <c r="A85" s="187"/>
       <c r="B85" s="184" t="s">
         <v>1408</v>
       </c>
-      <c r="C85" s="182" t="s">
+      <c r="C85" s="183" t="s">
         <v>1587</v>
       </c>
-      <c r="D85" s="185" t="s">
+      <c r="D85" s="177" t="s">
         <v>1469</v>
       </c>
-      <c r="E85" s="191">
+      <c r="E85" s="178">
         <v>43879</v>
       </c>
       <c r="F85" s="16" t="s">
@@ -29015,11 +29561,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="2:9">
-      <c r="B86" s="184"/>
-      <c r="C86" s="182"/>
-      <c r="D86" s="183"/>
-      <c r="E86" s="179"/>
+    <row r="86" spans="1:9">
+      <c r="A86" s="187"/>
+      <c r="B86" s="184" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C86" s="183" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D86" s="177" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E86" s="178">
+        <v>43879</v>
+      </c>
       <c r="F86" s="16" t="s">
         <v>13</v>
       </c>
@@ -29033,11 +29588,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="2:9">
-      <c r="B87" s="184"/>
-      <c r="C87" s="182"/>
-      <c r="D87" s="186"/>
-      <c r="E87" s="181"/>
+    <row r="87" spans="1:9">
+      <c r="A87" s="187"/>
+      <c r="B87" s="184" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C87" s="183" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D87" s="177" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E87" s="178">
+        <v>43879</v>
+      </c>
       <c r="F87" s="16" t="s">
         <v>110</v>
       </c>
@@ -29051,17 +29615,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="2:9">
+    <row r="88" spans="1:9">
+      <c r="A88" s="187"/>
       <c r="B88" s="184" t="s">
         <v>1429</v>
       </c>
-      <c r="C88" s="182" t="s">
+      <c r="C88" s="183" t="s">
         <v>1588</v>
       </c>
       <c r="D88" s="184" t="s">
         <v>1472</v>
       </c>
-      <c r="E88" s="190">
+      <c r="E88" s="185">
         <v>43887</v>
       </c>
       <c r="F88" s="16" t="s">
@@ -29077,11 +29642,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="2:9">
-      <c r="B89" s="184"/>
-      <c r="C89" s="182"/>
-      <c r="D89" s="184"/>
-      <c r="E89" s="182"/>
+    <row r="89" spans="1:9">
+      <c r="A89" s="187"/>
+      <c r="B89" s="184" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C89" s="183" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D89" s="184" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E89" s="185">
+        <v>43887</v>
+      </c>
       <c r="F89" s="16" t="s">
         <v>13</v>
       </c>
@@ -29095,11 +29669,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="2:9">
-      <c r="B90" s="184"/>
-      <c r="C90" s="182"/>
-      <c r="D90" s="184"/>
-      <c r="E90" s="182"/>
+    <row r="90" spans="1:9">
+      <c r="A90" s="187"/>
+      <c r="B90" s="184" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C90" s="183" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D90" s="184" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E90" s="185">
+        <v>43887</v>
+      </c>
       <c r="F90" s="16" t="s">
         <v>110</v>
       </c>
@@ -29113,17 +29696,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="2:9">
+    <row r="91" spans="1:9">
+      <c r="A91" s="187"/>
       <c r="B91" s="184" t="s">
         <v>1419</v>
       </c>
-      <c r="C91" s="182" t="s">
+      <c r="C91" s="183" t="s">
         <v>1590</v>
       </c>
       <c r="D91" s="184" t="s">
         <v>1475</v>
       </c>
-      <c r="E91" s="190">
+      <c r="E91" s="185">
         <v>43887</v>
       </c>
       <c r="F91" s="16" t="s">
@@ -29139,11 +29723,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="2:9">
-      <c r="B92" s="184"/>
-      <c r="C92" s="182"/>
-      <c r="D92" s="184"/>
-      <c r="E92" s="182"/>
+    <row r="92" spans="1:9">
+      <c r="A92" s="187"/>
+      <c r="B92" s="184" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C92" s="183" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D92" s="184" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E92" s="185">
+        <v>43887</v>
+      </c>
       <c r="F92" s="16" t="s">
         <v>879</v>
       </c>
@@ -29157,11 +29750,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="2:9">
-      <c r="B93" s="184"/>
-      <c r="C93" s="182"/>
-      <c r="D93" s="184"/>
-      <c r="E93" s="182"/>
+    <row r="93" spans="1:9">
+      <c r="A93" s="187"/>
+      <c r="B93" s="184" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C93" s="183" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D93" s="184" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E93" s="185">
+        <v>43887</v>
+      </c>
       <c r="F93" s="16" t="s">
         <v>13</v>
       </c>
@@ -29175,11 +29777,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="2:9">
-      <c r="B94" s="184"/>
-      <c r="C94" s="182"/>
-      <c r="D94" s="184"/>
-      <c r="E94" s="182"/>
+    <row r="94" spans="1:9">
+      <c r="A94" s="187"/>
+      <c r="B94" s="184" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C94" s="183" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D94" s="184" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E94" s="185">
+        <v>43887</v>
+      </c>
       <c r="F94" s="16" t="s">
         <v>110</v>
       </c>
@@ -29193,17 +29804,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="2:9">
+    <row r="95" spans="1:9">
+      <c r="A95" s="187"/>
       <c r="B95" s="184" t="s">
         <v>1430</v>
       </c>
-      <c r="C95" s="182" t="s">
+      <c r="C95" s="183" t="s">
         <v>1597</v>
       </c>
       <c r="D95" s="184" t="s">
         <v>1598</v>
       </c>
-      <c r="E95" s="190">
+      <c r="E95" s="185">
         <v>43887</v>
       </c>
       <c r="F95" s="16" t="s">
@@ -29219,11 +29831,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="2:9">
-      <c r="B96" s="184"/>
-      <c r="C96" s="182"/>
-      <c r="D96" s="184"/>
-      <c r="E96" s="182"/>
+    <row r="96" spans="1:9">
+      <c r="A96" s="187"/>
+      <c r="B96" s="184" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C96" s="183" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D96" s="184" t="s">
+        <v>1598</v>
+      </c>
+      <c r="E96" s="185">
+        <v>43887</v>
+      </c>
       <c r="F96" s="16" t="s">
         <v>879</v>
       </c>
@@ -29237,11 +29858,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="2:9">
-      <c r="B97" s="184"/>
-      <c r="C97" s="182"/>
-      <c r="D97" s="184"/>
-      <c r="E97" s="182"/>
+    <row r="97" spans="1:9">
+      <c r="A97" s="187"/>
+      <c r="B97" s="184" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C97" s="183" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D97" s="184" t="s">
+        <v>1598</v>
+      </c>
+      <c r="E97" s="185">
+        <v>43887</v>
+      </c>
       <c r="F97" s="16" t="s">
         <v>13</v>
       </c>
@@ -29255,11 +29885,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="2:9">
-      <c r="B98" s="184"/>
-      <c r="C98" s="182"/>
-      <c r="D98" s="184"/>
-      <c r="E98" s="182"/>
+    <row r="98" spans="1:9">
+      <c r="A98" s="187"/>
+      <c r="B98" s="184" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C98" s="183" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D98" s="184" t="s">
+        <v>1598</v>
+      </c>
+      <c r="E98" s="185">
+        <v>43887</v>
+      </c>
       <c r="F98" s="16" t="s">
         <v>110</v>
       </c>
@@ -29273,17 +29912,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="2:9">
+    <row r="99" spans="1:9" ht="13.8" customHeight="1">
+      <c r="A99" s="187"/>
       <c r="B99" s="184" t="s">
         <v>1435</v>
       </c>
-      <c r="C99" s="182" t="s">
+      <c r="C99" s="183" t="s">
         <v>1599</v>
       </c>
       <c r="D99" s="184" t="s">
         <v>1600</v>
       </c>
-      <c r="E99" s="190">
+      <c r="E99" s="185">
         <v>43889</v>
       </c>
       <c r="F99" s="16" t="s">
@@ -29299,11 +29939,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="2:9">
-      <c r="B100" s="184"/>
-      <c r="C100" s="182"/>
-      <c r="D100" s="184"/>
-      <c r="E100" s="182"/>
+    <row r="100" spans="1:9" ht="27.6">
+      <c r="A100" s="187"/>
+      <c r="B100" s="184" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C100" s="183" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D100" s="184" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E100" s="185">
+        <v>43889</v>
+      </c>
       <c r="F100" s="16" t="s">
         <v>879</v>
       </c>
@@ -29317,11 +29966,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="2:9">
-      <c r="B101" s="184"/>
-      <c r="C101" s="182"/>
-      <c r="D101" s="184"/>
-      <c r="E101" s="182"/>
+    <row r="101" spans="1:9" ht="27.6">
+      <c r="A101" s="187"/>
+      <c r="B101" s="184" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C101" s="183" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D101" s="184" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E101" s="185">
+        <v>43889</v>
+      </c>
       <c r="F101" s="16" t="s">
         <v>13</v>
       </c>
@@ -29335,11 +29993,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="2:9">
-      <c r="B102" s="184"/>
-      <c r="C102" s="182"/>
-      <c r="D102" s="184"/>
-      <c r="E102" s="182"/>
+    <row r="102" spans="1:9" ht="27.6">
+      <c r="A102" s="187"/>
+      <c r="B102" s="184" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C102" s="183" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D102" s="184" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E102" s="185">
+        <v>43889</v>
+      </c>
       <c r="F102" s="16" t="s">
         <v>110</v>
       </c>
@@ -29353,17 +30020,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="2:9">
+    <row r="103" spans="1:9">
+      <c r="A103" s="187"/>
       <c r="B103" s="184" t="s">
         <v>1376</v>
       </c>
-      <c r="C103" s="182" t="s">
+      <c r="C103" s="183" t="s">
         <v>1601</v>
       </c>
       <c r="D103" s="184" t="s">
         <v>1481</v>
       </c>
-      <c r="E103" s="190">
+      <c r="E103" s="185">
         <v>43889</v>
       </c>
       <c r="F103" s="16" t="s">
@@ -29379,11 +30047,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="2:9">
-      <c r="B104" s="184"/>
-      <c r="C104" s="182"/>
-      <c r="D104" s="184"/>
-      <c r="E104" s="182"/>
+    <row r="104" spans="1:9">
+      <c r="A104" s="187"/>
+      <c r="B104" s="184" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C104" s="183" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D104" s="184" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E104" s="185">
+        <v>43889</v>
+      </c>
       <c r="F104" s="16" t="s">
         <v>879</v>
       </c>
@@ -29397,11 +30074,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="2:9">
-      <c r="B105" s="184"/>
-      <c r="C105" s="182"/>
-      <c r="D105" s="184"/>
-      <c r="E105" s="182"/>
+    <row r="105" spans="1:9">
+      <c r="A105" s="187"/>
+      <c r="B105" s="184" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C105" s="183" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D105" s="184" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E105" s="185">
+        <v>43889</v>
+      </c>
       <c r="F105" s="16" t="s">
         <v>13</v>
       </c>
@@ -29415,11 +30101,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="2:9">
-      <c r="B106" s="184"/>
-      <c r="C106" s="182"/>
-      <c r="D106" s="184"/>
-      <c r="E106" s="182"/>
+    <row r="106" spans="1:9">
+      <c r="A106" s="187"/>
+      <c r="B106" s="184" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C106" s="183" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D106" s="184" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E106" s="185">
+        <v>43889</v>
+      </c>
       <c r="F106" s="16" t="s">
         <v>110</v>
       </c>
@@ -29433,17 +30128,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="2:9">
+    <row r="107" spans="1:9">
+      <c r="A107" s="187"/>
       <c r="B107" s="184" t="s">
         <v>1438</v>
       </c>
-      <c r="C107" s="182" t="s">
+      <c r="C107" s="183" t="s">
         <v>1602</v>
       </c>
       <c r="D107" s="184" t="s">
         <v>1486</v>
       </c>
-      <c r="E107" s="190">
+      <c r="E107" s="185">
         <v>43889</v>
       </c>
       <c r="F107" s="16" t="s">
@@ -29459,11 +30155,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="2:9">
-      <c r="B108" s="184"/>
-      <c r="C108" s="182"/>
-      <c r="D108" s="184"/>
-      <c r="E108" s="182"/>
+    <row r="108" spans="1:9">
+      <c r="A108" s="187"/>
+      <c r="B108" s="184" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C108" s="183" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D108" s="184" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E108" s="185">
+        <v>43889</v>
+      </c>
       <c r="F108" s="16" t="s">
         <v>879</v>
       </c>
@@ -29477,11 +30182,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="109" spans="2:9">
-      <c r="B109" s="184"/>
-      <c r="C109" s="182"/>
-      <c r="D109" s="184"/>
-      <c r="E109" s="182"/>
+    <row r="109" spans="1:9">
+      <c r="A109" s="187"/>
+      <c r="B109" s="184" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C109" s="183" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D109" s="184" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E109" s="185">
+        <v>43889</v>
+      </c>
       <c r="F109" s="16" t="s">
         <v>13</v>
       </c>
@@ -29495,11 +30209,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="2:9">
-      <c r="B110" s="184"/>
-      <c r="C110" s="182"/>
-      <c r="D110" s="184"/>
-      <c r="E110" s="182"/>
+    <row r="110" spans="1:9">
+      <c r="A110" s="187"/>
+      <c r="B110" s="184" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C110" s="183" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D110" s="184" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E110" s="185">
+        <v>43889</v>
+      </c>
       <c r="F110" s="16" t="s">
         <v>110</v>
       </c>
@@ -29513,17 +30236,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="2:9">
+    <row r="111" spans="1:9">
+      <c r="A111" s="187"/>
       <c r="B111" s="184" t="s">
         <v>1440</v>
       </c>
-      <c r="C111" s="182" t="s">
+      <c r="C111" s="183" t="s">
         <v>1603</v>
       </c>
       <c r="D111" s="184" t="s">
         <v>1495</v>
       </c>
-      <c r="E111" s="190">
+      <c r="E111" s="185">
         <v>43889</v>
       </c>
       <c r="F111" s="16" t="s">
@@ -29539,11 +30263,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="2:9">
-      <c r="B112" s="184"/>
-      <c r="C112" s="182"/>
-      <c r="D112" s="184"/>
-      <c r="E112" s="182"/>
+    <row r="112" spans="1:9">
+      <c r="A112" s="187"/>
+      <c r="B112" s="184" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C112" s="183" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D112" s="184" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E112" s="185">
+        <v>43889</v>
+      </c>
       <c r="F112" s="16" t="s">
         <v>879</v>
       </c>
@@ -29557,11 +30290,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" spans="2:9">
-      <c r="B113" s="184"/>
-      <c r="C113" s="182"/>
-      <c r="D113" s="184"/>
-      <c r="E113" s="182"/>
+    <row r="113" spans="1:9">
+      <c r="A113" s="187"/>
+      <c r="B113" s="184" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C113" s="183" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D113" s="184" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E113" s="185">
+        <v>43889</v>
+      </c>
       <c r="F113" s="16" t="s">
         <v>13</v>
       </c>
@@ -29575,11 +30317,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="2:9">
-      <c r="B114" s="184"/>
-      <c r="C114" s="182"/>
-      <c r="D114" s="184"/>
-      <c r="E114" s="182"/>
+    <row r="114" spans="1:9">
+      <c r="A114" s="187"/>
+      <c r="B114" s="184" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C114" s="183" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D114" s="184" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E114" s="185">
+        <v>43889</v>
+      </c>
       <c r="F114" s="16" t="s">
         <v>110</v>
       </c>
@@ -29593,17 +30344,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="2:9">
-      <c r="B115" s="182" t="s">
+    <row r="115" spans="1:9">
+      <c r="A115" s="187"/>
+      <c r="B115" s="183" t="s">
         <v>1443</v>
       </c>
-      <c r="C115" s="182" t="s">
+      <c r="C115" s="183" t="s">
         <v>1604</v>
       </c>
       <c r="D115" s="184" t="s">
         <v>1605</v>
       </c>
-      <c r="E115" s="190">
+      <c r="E115" s="185">
         <v>43906</v>
       </c>
       <c r="F115" s="16" t="s">
@@ -29619,11 +30371,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="116" spans="2:9">
-      <c r="B116" s="182"/>
-      <c r="C116" s="182"/>
-      <c r="D116" s="184"/>
-      <c r="E116" s="190"/>
+    <row r="116" spans="1:9">
+      <c r="A116" s="187"/>
+      <c r="B116" s="183" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C116" s="183" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D116" s="184" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E116" s="185">
+        <v>43906</v>
+      </c>
       <c r="F116" s="16" t="s">
         <v>13</v>
       </c>
@@ -29637,11 +30398,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="2:9">
-      <c r="B117" s="182"/>
-      <c r="C117" s="182"/>
-      <c r="D117" s="184"/>
-      <c r="E117" s="190"/>
+    <row r="117" spans="1:9">
+      <c r="A117" s="187"/>
+      <c r="B117" s="183" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C117" s="183" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D117" s="184" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E117" s="185">
+        <v>43906</v>
+      </c>
       <c r="F117" s="16" t="s">
         <v>110</v>
       </c>
@@ -29655,17 +30425,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="2:9">
-      <c r="B118" s="182" t="s">
+    <row r="118" spans="1:9">
+      <c r="A118" s="187"/>
+      <c r="B118" s="183" t="s">
         <v>1447</v>
       </c>
-      <c r="C118" s="182" t="s">
+      <c r="C118" s="183" t="s">
         <v>1609</v>
       </c>
       <c r="D118" s="184" t="s">
         <v>1610</v>
       </c>
-      <c r="E118" s="190">
+      <c r="E118" s="185">
         <v>43906</v>
       </c>
       <c r="F118" s="16" t="s">
@@ -29681,11 +30452,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="2:9">
-      <c r="B119" s="182"/>
-      <c r="C119" s="182"/>
-      <c r="D119" s="184"/>
-      <c r="E119" s="190"/>
+    <row r="119" spans="1:9">
+      <c r="A119" s="187"/>
+      <c r="B119" s="183" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C119" s="183" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D119" s="184" t="s">
+        <v>1610</v>
+      </c>
+      <c r="E119" s="185">
+        <v>43906</v>
+      </c>
       <c r="F119" s="16" t="s">
         <v>13</v>
       </c>
@@ -29699,11 +30479,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="2:9">
-      <c r="B120" s="182"/>
-      <c r="C120" s="182"/>
-      <c r="D120" s="184"/>
-      <c r="E120" s="190"/>
+    <row r="120" spans="1:9">
+      <c r="A120" s="187"/>
+      <c r="B120" s="183" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C120" s="183" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D120" s="184" t="s">
+        <v>1610</v>
+      </c>
+      <c r="E120" s="185">
+        <v>43906</v>
+      </c>
       <c r="F120" s="16" t="s">
         <v>110</v>
       </c>
@@ -29717,17 +30506,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" spans="2:9">
-      <c r="B121" s="180" t="s">
+    <row r="121" spans="1:9">
+      <c r="A121" s="187"/>
+      <c r="B121" s="176" t="s">
         <v>1611</v>
       </c>
-      <c r="C121" s="180" t="s">
+      <c r="C121" s="176" t="s">
         <v>1612</v>
       </c>
       <c r="D121" s="184" t="s">
         <v>1613</v>
       </c>
-      <c r="E121" s="190">
+      <c r="E121" s="185">
         <v>43906</v>
       </c>
       <c r="F121" s="16" t="s">
@@ -29743,11 +30533,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="122" spans="2:9">
-      <c r="B122" s="179"/>
-      <c r="C122" s="179"/>
-      <c r="D122" s="184"/>
-      <c r="E122" s="190"/>
+    <row r="122" spans="1:9">
+      <c r="A122" s="187"/>
+      <c r="B122" s="176" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C122" s="176" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D122" s="184" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E122" s="185">
+        <v>43906</v>
+      </c>
       <c r="F122" s="16" t="s">
         <v>13</v>
       </c>
@@ -29761,11 +30560,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="2:9">
-      <c r="B123" s="181"/>
-      <c r="C123" s="181"/>
-      <c r="D123" s="184"/>
-      <c r="E123" s="190"/>
+    <row r="123" spans="1:9">
+      <c r="A123" s="187"/>
+      <c r="B123" s="176" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C123" s="176" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D123" s="184" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E123" s="185">
+        <v>43906</v>
+      </c>
       <c r="F123" s="16" t="s">
         <v>110</v>
       </c>
@@ -29779,17 +30587,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="2:9">
-      <c r="B124" s="182" t="s">
+    <row r="124" spans="1:9">
+      <c r="A124" s="187"/>
+      <c r="B124" s="183" t="s">
         <v>1450</v>
       </c>
-      <c r="C124" s="182" t="s">
+      <c r="C124" s="183" t="s">
         <v>1617</v>
       </c>
       <c r="D124" s="184" t="s">
         <v>1618</v>
       </c>
-      <c r="E124" s="190">
+      <c r="E124" s="185">
         <v>43906</v>
       </c>
       <c r="F124" s="16" t="s">
@@ -29805,11 +30614,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="2:9">
-      <c r="B125" s="182"/>
-      <c r="C125" s="182"/>
-      <c r="D125" s="184"/>
-      <c r="E125" s="190"/>
+    <row r="125" spans="1:9">
+      <c r="A125" s="187"/>
+      <c r="B125" s="183" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C125" s="183" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D125" s="184" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E125" s="185">
+        <v>43906</v>
+      </c>
       <c r="F125" s="16" t="s">
         <v>13</v>
       </c>
@@ -29823,11 +30641,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="2:9">
-      <c r="B126" s="182"/>
-      <c r="C126" s="182"/>
-      <c r="D126" s="184"/>
-      <c r="E126" s="190"/>
+    <row r="126" spans="1:9">
+      <c r="A126" s="187"/>
+      <c r="B126" s="183" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C126" s="183" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D126" s="184" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E126" s="185">
+        <v>43906</v>
+      </c>
       <c r="F126" s="16" t="s">
         <v>110</v>
       </c>
@@ -29841,17 +30668,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="2:9">
-      <c r="B127" s="182" t="s">
+    <row r="127" spans="1:9">
+      <c r="A127" s="187"/>
+      <c r="B127" s="183" t="s">
         <v>1455</v>
       </c>
-      <c r="C127" s="182" t="s">
+      <c r="C127" s="183" t="s">
         <v>1619</v>
       </c>
       <c r="D127" s="184" t="s">
         <v>1620</v>
       </c>
-      <c r="E127" s="190">
+      <c r="E127" s="185">
         <v>43906</v>
       </c>
       <c r="F127" s="16" t="s">
@@ -29867,11 +30695,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="2:9">
-      <c r="B128" s="182"/>
-      <c r="C128" s="182"/>
-      <c r="D128" s="184"/>
-      <c r="E128" s="190"/>
+    <row r="128" spans="1:9">
+      <c r="A128" s="187"/>
+      <c r="B128" s="183" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C128" s="183" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D128" s="184" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E128" s="185">
+        <v>43906</v>
+      </c>
       <c r="F128" s="16" t="s">
         <v>13</v>
       </c>
@@ -29885,11 +30722,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="129" spans="2:9">
-      <c r="B129" s="182"/>
-      <c r="C129" s="182"/>
-      <c r="D129" s="184"/>
-      <c r="E129" s="190"/>
+    <row r="129" spans="1:9">
+      <c r="A129" s="187"/>
+      <c r="B129" s="183" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C129" s="183" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D129" s="184" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E129" s="185">
+        <v>43906</v>
+      </c>
       <c r="F129" s="16" t="s">
         <v>110</v>
       </c>
@@ -29903,17 +30749,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" spans="2:9">
-      <c r="B130" s="180" t="s">
+    <row r="130" spans="1:9">
+      <c r="A130" s="187"/>
+      <c r="B130" s="176" t="s">
         <v>1460</v>
       </c>
-      <c r="C130" s="180" t="s">
+      <c r="C130" s="176" t="s">
         <v>1621</v>
       </c>
       <c r="D130" s="184" t="s">
         <v>1622</v>
       </c>
-      <c r="E130" s="190">
+      <c r="E130" s="185">
         <v>43906</v>
       </c>
       <c r="F130" s="16" t="s">
@@ -29929,11 +30776,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="2:9">
-      <c r="B131" s="179"/>
-      <c r="C131" s="179"/>
-      <c r="D131" s="184"/>
-      <c r="E131" s="190"/>
+    <row r="131" spans="1:9">
+      <c r="A131" s="187"/>
+      <c r="B131" s="176" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C131" s="176" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D131" s="184" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E131" s="185">
+        <v>43906</v>
+      </c>
       <c r="F131" s="16" t="s">
         <v>13</v>
       </c>
@@ -29947,11 +30803,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" spans="2:9">
-      <c r="B132" s="181"/>
-      <c r="C132" s="181"/>
-      <c r="D132" s="184"/>
-      <c r="E132" s="190"/>
+    <row r="132" spans="1:9">
+      <c r="A132" s="187"/>
+      <c r="B132" s="176" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C132" s="176" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D132" s="184" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E132" s="185">
+        <v>43906</v>
+      </c>
       <c r="F132" s="16" t="s">
         <v>110</v>
       </c>
@@ -29965,17 +30830,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="133" spans="2:9">
-      <c r="B133" s="180" t="s">
+    <row r="133" spans="1:9">
+      <c r="A133" s="187"/>
+      <c r="B133" s="176" t="s">
         <v>1623</v>
       </c>
-      <c r="C133" s="180" t="s">
+      <c r="C133" s="176" t="s">
         <v>1624</v>
       </c>
       <c r="D133" s="184" t="s">
         <v>1625</v>
       </c>
-      <c r="E133" s="190">
+      <c r="E133" s="185">
         <v>43906</v>
       </c>
       <c r="F133" s="16" t="s">
@@ -29991,11 +30857,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" spans="2:9">
-      <c r="B134" s="179"/>
-      <c r="C134" s="179"/>
-      <c r="D134" s="184"/>
-      <c r="E134" s="190"/>
+    <row r="134" spans="1:9">
+      <c r="A134" s="187"/>
+      <c r="B134" s="176" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C134" s="176" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D134" s="184" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E134" s="185">
+        <v>43906</v>
+      </c>
       <c r="F134" s="16" t="s">
         <v>13</v>
       </c>
@@ -30009,11 +30884,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" spans="2:9">
-      <c r="B135" s="181"/>
-      <c r="C135" s="181"/>
-      <c r="D135" s="184"/>
-      <c r="E135" s="190"/>
+    <row r="135" spans="1:9">
+      <c r="A135" s="187"/>
+      <c r="B135" s="176" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C135" s="176" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D135" s="184" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E135" s="185">
+        <v>43906</v>
+      </c>
       <c r="F135" s="16" t="s">
         <v>110</v>
       </c>
@@ -30027,17 +30911,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" spans="2:9">
-      <c r="B136" s="182" t="s">
+    <row r="136" spans="1:9" ht="13.8" customHeight="1">
+      <c r="A136" s="187"/>
+      <c r="B136" s="183" t="s">
         <v>1578</v>
       </c>
-      <c r="C136" s="182" t="s">
+      <c r="C136" s="183" t="s">
         <v>1626</v>
       </c>
       <c r="D136" s="184" t="s">
         <v>1627</v>
       </c>
-      <c r="E136" s="190">
+      <c r="E136" s="185">
         <v>44019</v>
       </c>
       <c r="F136" s="16" t="s">
@@ -30053,11 +30938,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="2:9">
-      <c r="B137" s="182"/>
-      <c r="C137" s="182"/>
-      <c r="D137" s="184"/>
-      <c r="E137" s="182"/>
+    <row r="137" spans="1:9" ht="27.6">
+      <c r="A137" s="187"/>
+      <c r="B137" s="183" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C137" s="183" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D137" s="184" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E137" s="185">
+        <v>44019</v>
+      </c>
       <c r="F137" s="16" t="s">
         <v>13</v>
       </c>
@@ -30071,11 +30965,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="138" spans="2:9">
-      <c r="B138" s="182"/>
-      <c r="C138" s="182"/>
-      <c r="D138" s="184"/>
-      <c r="E138" s="182"/>
+    <row r="138" spans="1:9" ht="27.6">
+      <c r="A138" s="187"/>
+      <c r="B138" s="183" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C138" s="183" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D138" s="184" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E138" s="185">
+        <v>44019</v>
+      </c>
       <c r="F138" s="16" t="s">
         <v>110</v>
       </c>
@@ -30089,17 +30992,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" spans="2:9">
-      <c r="B139" s="182" t="s">
+    <row r="139" spans="1:9" ht="13.8" customHeight="1">
+      <c r="A139" s="187"/>
+      <c r="B139" s="183" t="s">
         <v>1580</v>
       </c>
-      <c r="C139" s="182" t="s">
+      <c r="C139" s="183" t="s">
         <v>1628</v>
       </c>
       <c r="D139" s="184" t="s">
         <v>1629</v>
       </c>
-      <c r="E139" s="190">
+      <c r="E139" s="185">
         <v>44022</v>
       </c>
       <c r="F139" s="16" t="s">
@@ -30115,11 +31019,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="2:9">
-      <c r="B140" s="182"/>
-      <c r="C140" s="182"/>
-      <c r="D140" s="184"/>
-      <c r="E140" s="190"/>
+    <row r="140" spans="1:9" ht="27.6">
+      <c r="A140" s="187"/>
+      <c r="B140" s="183" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C140" s="183" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D140" s="184" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E140" s="185">
+        <v>44022</v>
+      </c>
       <c r="F140" s="16" t="s">
         <v>879</v>
       </c>
@@ -30133,11 +31046,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="2:9">
-      <c r="B141" s="182"/>
-      <c r="C141" s="182"/>
-      <c r="D141" s="184"/>
-      <c r="E141" s="182"/>
+    <row r="141" spans="1:9" ht="27.6">
+      <c r="A141" s="187"/>
+      <c r="B141" s="183" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C141" s="183" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D141" s="184" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E141" s="185">
+        <v>44022</v>
+      </c>
       <c r="F141" s="16" t="s">
         <v>13</v>
       </c>
@@ -30151,11 +31073,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="142" spans="2:9">
-      <c r="B142" s="182"/>
-      <c r="C142" s="182"/>
-      <c r="D142" s="184"/>
-      <c r="E142" s="182"/>
+    <row r="142" spans="1:9" ht="27.6">
+      <c r="A142" s="187"/>
+      <c r="B142" s="183" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C142" s="183" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D142" s="184" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E142" s="185">
+        <v>44022</v>
+      </c>
       <c r="F142" s="16" t="s">
         <v>110</v>
       </c>
@@ -30169,17 +31100,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="143" spans="2:9">
-      <c r="B143" s="182" t="s">
+    <row r="143" spans="1:9">
+      <c r="A143" s="187"/>
+      <c r="B143" s="183" t="s">
         <v>1463</v>
       </c>
-      <c r="C143" s="182" t="s">
+      <c r="C143" s="183" t="s">
         <v>1634</v>
       </c>
       <c r="D143" s="184" t="s">
         <v>1635</v>
       </c>
-      <c r="E143" s="190">
+      <c r="E143" s="185">
         <v>44022</v>
       </c>
       <c r="F143" s="16" t="s">
@@ -30195,11 +31127,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" spans="2:9">
-      <c r="B144" s="182"/>
-      <c r="C144" s="182"/>
-      <c r="D144" s="184"/>
-      <c r="E144" s="182"/>
+    <row r="144" spans="1:9">
+      <c r="A144" s="187"/>
+      <c r="B144" s="183" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C144" s="183" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D144" s="184" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E144" s="185">
+        <v>44022</v>
+      </c>
       <c r="F144" s="16" t="s">
         <v>879</v>
       </c>
@@ -30213,11 +31154,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="2:9">
-      <c r="B145" s="182"/>
-      <c r="C145" s="182"/>
-      <c r="D145" s="184"/>
-      <c r="E145" s="182"/>
+    <row r="145" spans="1:9">
+      <c r="A145" s="187"/>
+      <c r="B145" s="183" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C145" s="183" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D145" s="184" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E145" s="185">
+        <v>44022</v>
+      </c>
       <c r="F145" s="16" t="s">
         <v>13</v>
       </c>
@@ -30231,11 +31181,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" spans="2:9">
-      <c r="B146" s="182"/>
-      <c r="C146" s="182"/>
-      <c r="D146" s="184"/>
-      <c r="E146" s="182"/>
+    <row r="146" spans="1:9">
+      <c r="A146" s="187"/>
+      <c r="B146" s="183" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C146" s="183" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D146" s="184" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E146" s="185">
+        <v>44022</v>
+      </c>
       <c r="F146" s="16" t="s">
         <v>110</v>
       </c>
@@ -30249,17 +31208,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="2:9">
-      <c r="B147" s="182" t="s">
+    <row r="147" spans="1:9" ht="13.8" customHeight="1">
+      <c r="A147" s="187"/>
+      <c r="B147" s="183" t="s">
         <v>1466</v>
       </c>
-      <c r="C147" s="182" t="s">
+      <c r="C147" s="183" t="s">
         <v>1636</v>
       </c>
       <c r="D147" s="184" t="s">
         <v>1244</v>
       </c>
-      <c r="E147" s="190">
+      <c r="E147" s="185">
         <v>44022</v>
       </c>
       <c r="F147" s="16" t="s">
@@ -30275,11 +31235,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="148" spans="2:9">
-      <c r="B148" s="182"/>
-      <c r="C148" s="182"/>
-      <c r="D148" s="184"/>
-      <c r="E148" s="182"/>
+    <row r="148" spans="1:9" ht="27.6">
+      <c r="A148" s="187"/>
+      <c r="B148" s="183" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C148" s="183" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D148" s="184" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E148" s="185">
+        <v>44022</v>
+      </c>
       <c r="F148" s="16" t="s">
         <v>879</v>
       </c>
@@ -30293,11 +31262,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="2:9">
-      <c r="B149" s="182"/>
-      <c r="C149" s="182"/>
-      <c r="D149" s="184"/>
-      <c r="E149" s="182"/>
+    <row r="149" spans="1:9" ht="27.6">
+      <c r="A149" s="187"/>
+      <c r="B149" s="183" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C149" s="183" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D149" s="184" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E149" s="185">
+        <v>44022</v>
+      </c>
       <c r="F149" s="16" t="s">
         <v>13</v>
       </c>
@@ -30311,11 +31289,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="150" spans="2:9">
-      <c r="B150" s="182"/>
-      <c r="C150" s="182"/>
-      <c r="D150" s="184"/>
-      <c r="E150" s="182"/>
+    <row r="150" spans="1:9" ht="27.6">
+      <c r="A150" s="187"/>
+      <c r="B150" s="183" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C150" s="183" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D150" s="184" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E150" s="185">
+        <v>44022</v>
+      </c>
       <c r="F150" s="16" t="s">
         <v>110</v>
       </c>
@@ -30329,17 +31316,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="2:9">
-      <c r="B151" s="182" t="s">
+    <row r="151" spans="1:9">
+      <c r="A151" s="187"/>
+      <c r="B151" s="183" t="s">
         <v>1469</v>
       </c>
-      <c r="C151" s="182" t="s">
+      <c r="C151" s="183" t="s">
         <v>1637</v>
       </c>
       <c r="D151" s="184" t="s">
         <v>1461</v>
       </c>
-      <c r="E151" s="190">
+      <c r="E151" s="185">
         <v>44022</v>
       </c>
       <c r="F151" s="16" t="s">
@@ -30355,11 +31343,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="152" spans="2:9">
-      <c r="B152" s="182"/>
-      <c r="C152" s="182"/>
-      <c r="D152" s="184"/>
-      <c r="E152" s="182"/>
+    <row r="152" spans="1:9">
+      <c r="A152" s="187"/>
+      <c r="B152" s="183" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C152" s="183" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D152" s="184" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E152" s="185">
+        <v>44022</v>
+      </c>
       <c r="F152" s="16" t="s">
         <v>879</v>
       </c>
@@ -30373,11 +31370,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" spans="2:9">
-      <c r="B153" s="182"/>
-      <c r="C153" s="182"/>
-      <c r="D153" s="184"/>
-      <c r="E153" s="182"/>
+    <row r="153" spans="1:9">
+      <c r="A153" s="187"/>
+      <c r="B153" s="183" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C153" s="183" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D153" s="184" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E153" s="185">
+        <v>44022</v>
+      </c>
       <c r="F153" s="16" t="s">
         <v>13</v>
       </c>
@@ -30391,11 +31397,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" spans="2:9">
-      <c r="B154" s="182"/>
-      <c r="C154" s="182"/>
-      <c r="D154" s="184"/>
-      <c r="E154" s="182"/>
+    <row r="154" spans="1:9">
+      <c r="A154" s="187"/>
+      <c r="B154" s="183" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C154" s="183" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D154" s="184" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E154" s="185">
+        <v>44022</v>
+      </c>
       <c r="F154" s="16" t="s">
         <v>110</v>
       </c>
@@ -30409,17 +31424,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" spans="2:9">
-      <c r="B155" s="182" t="s">
+    <row r="155" spans="1:9" ht="13.8" customHeight="1">
+      <c r="A155" s="187"/>
+      <c r="B155" s="183" t="s">
         <v>1424</v>
       </c>
-      <c r="C155" s="182" t="s">
+      <c r="C155" s="183" t="s">
         <v>1638</v>
       </c>
       <c r="D155" s="184" t="s">
         <v>1497</v>
       </c>
-      <c r="E155" s="190">
+      <c r="E155" s="185">
         <v>44022</v>
       </c>
       <c r="F155" s="16" t="s">
@@ -30435,11 +31451,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="2:9">
-      <c r="B156" s="182"/>
-      <c r="C156" s="182"/>
-      <c r="D156" s="184"/>
-      <c r="E156" s="182"/>
+    <row r="156" spans="1:9" ht="27.6">
+      <c r="A156" s="187"/>
+      <c r="B156" s="183" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C156" s="183" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D156" s="184" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E156" s="185">
+        <v>44022</v>
+      </c>
       <c r="F156" s="16" t="s">
         <v>879</v>
       </c>
@@ -30453,11 +31478,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="2:9">
-      <c r="B157" s="182"/>
-      <c r="C157" s="182"/>
-      <c r="D157" s="184"/>
-      <c r="E157" s="182"/>
+    <row r="157" spans="1:9" ht="27.6">
+      <c r="A157" s="187"/>
+      <c r="B157" s="183" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C157" s="183" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D157" s="184" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E157" s="185">
+        <v>44022</v>
+      </c>
       <c r="F157" s="16" t="s">
         <v>13</v>
       </c>
@@ -30471,11 +31505,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="158" spans="2:9">
-      <c r="B158" s="182"/>
-      <c r="C158" s="182"/>
-      <c r="D158" s="184"/>
-      <c r="E158" s="182"/>
+    <row r="158" spans="1:9" ht="27.6">
+      <c r="A158" s="187"/>
+      <c r="B158" s="183" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C158" s="183" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D158" s="184" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E158" s="185">
+        <v>44022</v>
+      </c>
       <c r="F158" s="16" t="s">
         <v>110</v>
       </c>
@@ -30489,17 +31532,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="2:9">
-      <c r="B159" s="182" t="s">
+    <row r="159" spans="1:9">
+      <c r="A159" s="187"/>
+      <c r="B159" s="183" t="s">
         <v>1639</v>
       </c>
-      <c r="C159" s="182" t="s">
+      <c r="C159" s="183" t="s">
         <v>1640</v>
       </c>
       <c r="D159" s="184" t="s">
         <v>1483</v>
       </c>
-      <c r="E159" s="190">
+      <c r="E159" s="185">
         <v>44022</v>
       </c>
       <c r="F159" s="16" t="s">
@@ -30515,11 +31559,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="2:9">
-      <c r="B160" s="182"/>
-      <c r="C160" s="182"/>
-      <c r="D160" s="184"/>
-      <c r="E160" s="182"/>
+    <row r="160" spans="1:9">
+      <c r="A160" s="187"/>
+      <c r="B160" s="183" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C160" s="183" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D160" s="184" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E160" s="185">
+        <v>44022</v>
+      </c>
       <c r="F160" s="16" t="s">
         <v>879</v>
       </c>
@@ -30533,11 +31586,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="161" spans="2:9">
-      <c r="B161" s="182"/>
-      <c r="C161" s="182"/>
-      <c r="D161" s="184"/>
-      <c r="E161" s="182"/>
+    <row r="161" spans="1:9">
+      <c r="A161" s="187"/>
+      <c r="B161" s="183" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C161" s="183" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D161" s="184" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E161" s="185">
+        <v>44022</v>
+      </c>
       <c r="F161" s="16" t="s">
         <v>13</v>
       </c>
@@ -30551,11 +31613,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" spans="2:9">
-      <c r="B162" s="182"/>
-      <c r="C162" s="182"/>
-      <c r="D162" s="184"/>
-      <c r="E162" s="182"/>
+    <row r="162" spans="1:9">
+      <c r="A162" s="187"/>
+      <c r="B162" s="183" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C162" s="183" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D162" s="184" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E162" s="185">
+        <v>44022</v>
+      </c>
       <c r="F162" s="16" t="s">
         <v>110</v>
       </c>
@@ -30569,17 +31640,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" spans="2:9">
-      <c r="B163" s="182" t="s">
+    <row r="163" spans="1:9">
+      <c r="A163" s="187"/>
+      <c r="B163" s="183" t="s">
         <v>1472</v>
       </c>
-      <c r="C163" s="182" t="s">
+      <c r="C163" s="183" t="s">
         <v>1641</v>
       </c>
       <c r="D163" s="184" t="s">
         <v>1642</v>
       </c>
-      <c r="E163" s="190">
+      <c r="E163" s="185">
         <v>44022</v>
       </c>
       <c r="F163" s="16" t="s">
@@ -30595,11 +31667,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="164" spans="2:9">
-      <c r="B164" s="182"/>
-      <c r="C164" s="182"/>
-      <c r="D164" s="184"/>
-      <c r="E164" s="182"/>
+    <row r="164" spans="1:9">
+      <c r="A164" s="187"/>
+      <c r="B164" s="183" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C164" s="183" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D164" s="184" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E164" s="185">
+        <v>44022</v>
+      </c>
       <c r="F164" s="16" t="s">
         <v>879</v>
       </c>
@@ -30613,11 +31694,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" spans="2:9">
-      <c r="B165" s="182"/>
-      <c r="C165" s="182"/>
-      <c r="D165" s="184"/>
-      <c r="E165" s="182"/>
+    <row r="165" spans="1:9">
+      <c r="A165" s="187"/>
+      <c r="B165" s="183" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C165" s="183" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D165" s="184" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E165" s="185">
+        <v>44022</v>
+      </c>
       <c r="F165" s="16" t="s">
         <v>13</v>
       </c>
@@ -30631,11 +31721,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="2:9">
-      <c r="B166" s="182"/>
-      <c r="C166" s="182"/>
-      <c r="D166" s="184"/>
-      <c r="E166" s="182"/>
+    <row r="166" spans="1:9">
+      <c r="A166" s="187"/>
+      <c r="B166" s="183" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C166" s="183" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D166" s="184" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E166" s="185">
+        <v>44022</v>
+      </c>
       <c r="F166" s="16" t="s">
         <v>110</v>
       </c>
@@ -30649,17 +31748,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="2:9">
-      <c r="B167" s="182" t="s">
+    <row r="167" spans="1:9">
+      <c r="A167" s="187"/>
+      <c r="B167" s="183" t="s">
         <v>1475</v>
       </c>
-      <c r="C167" s="182" t="s">
+      <c r="C167" s="183" t="s">
         <v>1643</v>
       </c>
       <c r="D167" s="184" t="s">
         <v>1487</v>
       </c>
-      <c r="E167" s="190">
+      <c r="E167" s="185">
         <v>44022</v>
       </c>
       <c r="F167" s="16" t="s">
@@ -30675,11 +31775,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="2:9">
-      <c r="B168" s="182"/>
-      <c r="C168" s="182"/>
-      <c r="D168" s="184"/>
-      <c r="E168" s="182"/>
+    <row r="168" spans="1:9">
+      <c r="A168" s="187"/>
+      <c r="B168" s="183" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C168" s="183" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D168" s="184" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E168" s="185">
+        <v>44022</v>
+      </c>
       <c r="F168" s="16" t="s">
         <v>879</v>
       </c>
@@ -30693,11 +31802,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="2:9">
-      <c r="B169" s="182"/>
-      <c r="C169" s="182"/>
-      <c r="D169" s="184"/>
-      <c r="E169" s="182"/>
+    <row r="169" spans="1:9">
+      <c r="A169" s="187"/>
+      <c r="B169" s="183" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C169" s="183" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D169" s="184" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E169" s="185">
+        <v>44022</v>
+      </c>
       <c r="F169" s="16" t="s">
         <v>13</v>
       </c>
@@ -30711,11 +31829,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="170" spans="2:9">
-      <c r="B170" s="182"/>
-      <c r="C170" s="182"/>
-      <c r="D170" s="184"/>
-      <c r="E170" s="182"/>
+    <row r="170" spans="1:9">
+      <c r="A170" s="187"/>
+      <c r="B170" s="183" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C170" s="183" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D170" s="184" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E170" s="185">
+        <v>44022</v>
+      </c>
       <c r="F170" s="16" t="s">
         <v>110</v>
       </c>
@@ -30730,231 +31857,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="222">
-    <mergeCell ref="E147:E150"/>
-    <mergeCell ref="E151:E154"/>
-    <mergeCell ref="E155:E158"/>
-    <mergeCell ref="E159:E162"/>
-    <mergeCell ref="E163:E166"/>
-    <mergeCell ref="E167:E170"/>
-    <mergeCell ref="E118:E120"/>
-    <mergeCell ref="E121:E123"/>
-    <mergeCell ref="E124:E126"/>
-    <mergeCell ref="E127:E129"/>
-    <mergeCell ref="E130:E132"/>
-    <mergeCell ref="E133:E135"/>
-    <mergeCell ref="E136:E138"/>
-    <mergeCell ref="E139:E142"/>
-    <mergeCell ref="E143:E146"/>
-    <mergeCell ref="E85:E87"/>
-    <mergeCell ref="E88:E90"/>
-    <mergeCell ref="E91:E94"/>
-    <mergeCell ref="E95:E98"/>
-    <mergeCell ref="E99:E102"/>
-    <mergeCell ref="E103:E106"/>
-    <mergeCell ref="E107:E110"/>
-    <mergeCell ref="E111:E114"/>
-    <mergeCell ref="E115:E117"/>
-    <mergeCell ref="E58:E60"/>
-    <mergeCell ref="E61:E63"/>
-    <mergeCell ref="E64:E66"/>
-    <mergeCell ref="E67:E69"/>
-    <mergeCell ref="E70:E72"/>
-    <mergeCell ref="E73:E75"/>
-    <mergeCell ref="E76:E78"/>
-    <mergeCell ref="E79:E81"/>
-    <mergeCell ref="E82:E84"/>
-    <mergeCell ref="D147:D150"/>
-    <mergeCell ref="D151:D154"/>
-    <mergeCell ref="D155:D158"/>
-    <mergeCell ref="D159:D162"/>
-    <mergeCell ref="D163:D166"/>
-    <mergeCell ref="D167:D170"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="E45:E47"/>
-    <mergeCell ref="E48:E50"/>
-    <mergeCell ref="E51:E53"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="D118:D120"/>
-    <mergeCell ref="D121:D123"/>
-    <mergeCell ref="D124:D126"/>
-    <mergeCell ref="D127:D129"/>
-    <mergeCell ref="D130:D132"/>
-    <mergeCell ref="D133:D135"/>
-    <mergeCell ref="D136:D138"/>
-    <mergeCell ref="D139:D142"/>
-    <mergeCell ref="D143:D146"/>
-    <mergeCell ref="D85:D87"/>
-    <mergeCell ref="D88:D90"/>
-    <mergeCell ref="D91:D94"/>
-    <mergeCell ref="D95:D98"/>
-    <mergeCell ref="D99:D102"/>
-    <mergeCell ref="D103:D106"/>
-    <mergeCell ref="D107:D110"/>
-    <mergeCell ref="D111:D114"/>
-    <mergeCell ref="D115:D117"/>
-    <mergeCell ref="D58:D60"/>
-    <mergeCell ref="D61:D63"/>
-    <mergeCell ref="D64:D66"/>
-    <mergeCell ref="D67:D69"/>
-    <mergeCell ref="D70:D72"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="D79:D81"/>
-    <mergeCell ref="D82:D84"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D45:D47"/>
-    <mergeCell ref="D48:D50"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="D54:D57"/>
-    <mergeCell ref="C136:C138"/>
-    <mergeCell ref="C139:C142"/>
-    <mergeCell ref="C143:C146"/>
-    <mergeCell ref="C147:C150"/>
-    <mergeCell ref="C151:C154"/>
-    <mergeCell ref="C155:C158"/>
-    <mergeCell ref="C159:C162"/>
-    <mergeCell ref="C163:C166"/>
-    <mergeCell ref="C167:C170"/>
-    <mergeCell ref="C107:C110"/>
-    <mergeCell ref="C111:C114"/>
-    <mergeCell ref="C115:C117"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="C121:C123"/>
-    <mergeCell ref="C124:C126"/>
-    <mergeCell ref="C127:C129"/>
-    <mergeCell ref="C130:C132"/>
-    <mergeCell ref="C133:C135"/>
-    <mergeCell ref="C73:C78"/>
-    <mergeCell ref="C79:C81"/>
-    <mergeCell ref="C82:C84"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="C88:C90"/>
-    <mergeCell ref="C91:C94"/>
-    <mergeCell ref="C95:C98"/>
-    <mergeCell ref="C99:C102"/>
-    <mergeCell ref="C103:C106"/>
-    <mergeCell ref="B163:B166"/>
-    <mergeCell ref="B167:B170"/>
-    <mergeCell ref="C3:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="C61:C63"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="C67:C69"/>
-    <mergeCell ref="C70:C72"/>
-    <mergeCell ref="B130:B132"/>
-    <mergeCell ref="B133:B135"/>
-    <mergeCell ref="B136:B138"/>
-    <mergeCell ref="B139:B142"/>
-    <mergeCell ref="B143:B146"/>
-    <mergeCell ref="B147:B150"/>
-    <mergeCell ref="B151:B154"/>
-    <mergeCell ref="B155:B158"/>
-    <mergeCell ref="B159:B162"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
-    <mergeCell ref="B107:B110"/>
-    <mergeCell ref="B111:B114"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="B124:B126"/>
-    <mergeCell ref="B127:B129"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B70:B72"/>
-    <mergeCell ref="B73:B78"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="B88:B90"/>
-    <mergeCell ref="B91:B94"/>
-    <mergeCell ref="B95:B98"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="B3:B8"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A54:A57"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D27:D29"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30978,17 +31886,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="194" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="197"/>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197"/>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="197"/>
+      <c r="B1" s="195"/>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
     </row>
     <row r="2" spans="1:9" ht="19.95" customHeight="1">
       <c r="A2" s="120" t="s">
@@ -31020,7 +31928,7 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="198"/>
+      <c r="A3" s="196"/>
       <c r="B3" s="28" t="s">
         <v>30</v>
       </c>
@@ -31047,7 +31955,7 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="198"/>
+      <c r="A4" s="196"/>
       <c r="B4" s="28" t="s">
         <v>30</v>
       </c>
@@ -31265,17 +32173,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27" customHeight="1">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="197" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
     </row>
     <row r="2" spans="1:11" ht="19.95" customHeight="1">
       <c r="A2" s="64" t="s">
@@ -31307,7 +32215,7 @@
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="201">
+      <c r="A3" s="199">
         <v>1</v>
       </c>
       <c r="B3" s="29" t="s">
@@ -31336,7 +32244,7 @@
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="202"/>
+      <c r="A4" s="200"/>
       <c r="B4" s="29" t="s">
         <v>57</v>
       </c>
@@ -32403,17 +33311,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27" customHeight="1">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="194" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="197"/>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197"/>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="197"/>
+      <c r="B1" s="195"/>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
     </row>
     <row r="2" spans="1:11" ht="19.95" customHeight="1">
       <c r="A2" s="45" t="s">
@@ -32673,7 +33581,7 @@
       <c r="I10" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="J10" s="210" t="s">
+      <c r="J10" s="201" t="s">
         <v>194</v>
       </c>
     </row>
@@ -32705,7 +33613,7 @@
       <c r="I11" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="J11" s="210"/>
+      <c r="J11" s="201"/>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
       <c r="A12" s="18">
@@ -32735,7 +33643,7 @@
       <c r="I12" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="J12" s="210"/>
+      <c r="J12" s="201"/>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1">
       <c r="A13" s="17">
@@ -33575,10 +34483,10 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="48"/>
-      <c r="B43" s="205" t="s">
+      <c r="B43" s="210" t="s">
         <v>225</v>
       </c>
-      <c r="C43" s="208" t="s">
+      <c r="C43" s="213" t="s">
         <v>226</v>
       </c>
       <c r="D43" s="42" t="s">
@@ -33602,8 +34510,8 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="48"/>
-      <c r="B44" s="206"/>
-      <c r="C44" s="209"/>
+      <c r="B44" s="211"/>
+      <c r="C44" s="214"/>
       <c r="D44" s="42" t="s">
         <v>227</v>
       </c>
@@ -34241,10 +35149,10 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="48"/>
-      <c r="B67" s="206" t="s">
+      <c r="B67" s="211" t="s">
         <v>260</v>
       </c>
-      <c r="C67" s="187" t="s">
+      <c r="C67" s="204" t="s">
         <v>261</v>
       </c>
       <c r="D67" s="18" t="s">
@@ -34268,8 +35176,8 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="48"/>
-      <c r="B68" s="207"/>
-      <c r="C68" s="188"/>
+      <c r="B68" s="212"/>
+      <c r="C68" s="215"/>
       <c r="D68" s="28" t="s">
         <v>263</v>
       </c>
@@ -34317,7 +35225,7 @@
       </c>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" s="203">
+      <c r="A70" s="208">
         <v>29</v>
       </c>
       <c r="B70" s="149" t="s">
@@ -34346,7 +35254,7 @@
       </c>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="204"/>
+      <c r="A71" s="209"/>
       <c r="B71" s="149" t="s">
         <v>264</v>
       </c>
@@ -34375,7 +35283,7 @@
       <c r="K71" s="59"/>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="204"/>
+      <c r="A72" s="209"/>
       <c r="B72" s="149" t="s">
         <v>264</v>
       </c>
@@ -34404,7 +35312,7 @@
       <c r="K72" s="59"/>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="204"/>
+      <c r="A73" s="209"/>
       <c r="B73" s="149" t="s">
         <v>264</v>
       </c>
@@ -34606,10 +35514,10 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="50"/>
-      <c r="B80" s="213" t="s">
+      <c r="B80" s="205" t="s">
         <v>205</v>
       </c>
-      <c r="C80" s="211" t="s">
+      <c r="C80" s="202" t="s">
         <v>103</v>
       </c>
       <c r="D80" s="32" t="s">
@@ -34635,8 +35543,8 @@
       <c r="A81" s="50">
         <v>36</v>
       </c>
-      <c r="B81" s="213"/>
-      <c r="C81" s="211"/>
+      <c r="B81" s="205"/>
+      <c r="C81" s="202"/>
       <c r="D81" s="32" t="s">
         <v>276</v>
       </c>
@@ -34658,10 +35566,10 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="51"/>
-      <c r="B82" s="214" t="s">
+      <c r="B82" s="206" t="s">
         <v>277</v>
       </c>
-      <c r="C82" s="212" t="s">
+      <c r="C82" s="203" t="s">
         <v>278</v>
       </c>
       <c r="D82" s="32" t="s">
@@ -34687,8 +35595,8 @@
       <c r="A83" s="51">
         <v>37</v>
       </c>
-      <c r="B83" s="215"/>
-      <c r="C83" s="187"/>
+      <c r="B83" s="207"/>
+      <c r="C83" s="204"/>
       <c r="D83" s="42" t="s">
         <v>279</v>
       </c>
@@ -36373,17 +37281,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="J10:J12"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B82:B83"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A70:A73"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="B67:B68"/>
     <mergeCell ref="C43:C44"/>
     <mergeCell ref="C67:C68"/>
+    <mergeCell ref="J10:J12"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="B82:B83"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -36415,17 +37323,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="197" t="s">
         <v>382</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
     </row>
     <row r="2" spans="1:9" ht="19.95" customHeight="1">
       <c r="A2" s="60" t="s">
@@ -36835,7 +37743,7 @@
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="201"/>
+      <c r="A17" s="199"/>
       <c r="B17" s="139" t="s">
         <v>399</v>
       </c>
@@ -36862,7 +37770,7 @@
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="202"/>
+      <c r="A18" s="200"/>
       <c r="B18" s="139" t="s">
         <v>399</v>
       </c>
@@ -37483,7 +38391,7 @@
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="201"/>
+      <c r="A41" s="199"/>
       <c r="B41" s="139" t="s">
         <v>432</v>
       </c>
@@ -37510,7 +38418,7 @@
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="202"/>
+      <c r="A42" s="200"/>
       <c r="B42" s="139" t="s">
         <v>432</v>
       </c>
@@ -37564,7 +38472,7 @@
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="201"/>
+      <c r="A44" s="199"/>
       <c r="B44" s="139" t="s">
         <v>195</v>
       </c>
@@ -37591,7 +38499,7 @@
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="202"/>
+      <c r="A45" s="200"/>
       <c r="B45" s="139" t="s">
         <v>195</v>
       </c>
@@ -37618,7 +38526,7 @@
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="198"/>
+      <c r="A46" s="196"/>
       <c r="B46" s="151" t="s">
         <v>304</v>
       </c>
@@ -37645,7 +38553,7 @@
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="198"/>
+      <c r="A47" s="196"/>
       <c r="B47" s="151" t="s">
         <v>304</v>
       </c>
@@ -37778,7 +38686,7 @@
       <c r="I51" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="J51" s="210" t="s">
+      <c r="J51" s="201" t="s">
         <v>452</v>
       </c>
     </row>
@@ -37808,7 +38716,7 @@
       <c r="I52" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="J52" s="210"/>
+      <c r="J52" s="201"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="51"/>
@@ -38378,7 +39286,7 @@
       </c>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="201"/>
+      <c r="A74" s="199"/>
       <c r="B74" s="158" t="s">
         <v>486</v>
       </c>
@@ -38405,7 +39313,7 @@
       </c>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="202"/>
+      <c r="A75" s="200"/>
       <c r="B75" s="158" t="s">
         <v>486</v>
       </c>
@@ -38675,7 +39583,7 @@
       </c>
     </row>
     <row r="85" spans="1:9" ht="13.8" customHeight="1">
-      <c r="A85" s="198"/>
+      <c r="A85" s="196"/>
       <c r="B85" s="151" t="s">
         <v>454</v>
       </c>
@@ -38702,7 +39610,7 @@
       </c>
     </row>
     <row r="86" spans="1:9" ht="27.6">
-      <c r="A86" s="198"/>
+      <c r="A86" s="196"/>
       <c r="B86" s="151" t="s">
         <v>454</v>
       </c>
@@ -38729,7 +39637,7 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="27.6">
-      <c r="A87" s="198"/>
+      <c r="A87" s="196"/>
       <c r="B87" s="151" t="s">
         <v>454</v>
       </c>
@@ -38756,7 +39664,7 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="27.6">
-      <c r="A88" s="198"/>
+      <c r="A88" s="196"/>
       <c r="B88" s="151" t="s">
         <v>454</v>
       </c>
@@ -38783,7 +39691,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="27.6">
-      <c r="A89" s="198"/>
+      <c r="A89" s="196"/>
       <c r="B89" s="151" t="s">
         <v>454</v>
       </c>
@@ -38810,7 +39718,7 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="27.6">
-      <c r="A90" s="198"/>
+      <c r="A90" s="196"/>
       <c r="B90" s="151" t="s">
         <v>454</v>
       </c>
@@ -38837,7 +39745,7 @@
       </c>
     </row>
     <row r="91" spans="1:9" ht="27.6">
-      <c r="A91" s="198"/>
+      <c r="A91" s="196"/>
       <c r="B91" s="151" t="s">
         <v>454</v>
       </c>
@@ -38864,7 +39772,7 @@
       </c>
     </row>
     <row r="92" spans="1:9">
-      <c r="A92" s="198"/>
+      <c r="A92" s="196"/>
       <c r="B92" s="151" t="s">
         <v>464</v>
       </c>
@@ -38891,7 +39799,7 @@
       </c>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="198"/>
+      <c r="A93" s="196"/>
       <c r="B93" s="151" t="s">
         <v>464</v>
       </c>
@@ -38918,7 +39826,7 @@
       </c>
     </row>
     <row r="94" spans="1:9">
-      <c r="A94" s="198"/>
+      <c r="A94" s="196"/>
       <c r="B94" s="151" t="s">
         <v>464</v>
       </c>
@@ -39161,7 +40069,7 @@
       </c>
     </row>
     <row r="103" spans="1:21">
-      <c r="A103" s="201"/>
+      <c r="A103" s="199"/>
       <c r="B103" s="139" t="s">
         <v>490</v>
       </c>
@@ -39188,7 +40096,7 @@
       </c>
     </row>
     <row r="104" spans="1:21">
-      <c r="A104" s="218"/>
+      <c r="A104" s="216"/>
       <c r="B104" s="139" t="s">
         <v>490</v>
       </c>
@@ -39215,7 +40123,7 @@
       </c>
     </row>
     <row r="105" spans="1:21">
-      <c r="A105" s="218"/>
+      <c r="A105" s="216"/>
       <c r="B105" s="139" t="s">
         <v>490</v>
       </c>
@@ -39242,7 +40150,7 @@
       </c>
     </row>
     <row r="106" spans="1:21">
-      <c r="A106" s="218"/>
+      <c r="A106" s="216"/>
       <c r="B106" s="139" t="s">
         <v>490</v>
       </c>
@@ -39323,7 +40231,7 @@
       </c>
     </row>
     <row r="109" spans="1:21" s="57" customFormat="1">
-      <c r="A109" s="198"/>
+      <c r="A109" s="196"/>
       <c r="B109" s="151" t="s">
         <v>491</v>
       </c>
@@ -39362,7 +40270,7 @@
       <c r="U109" s="84"/>
     </row>
     <row r="110" spans="1:21">
-      <c r="A110" s="198"/>
+      <c r="A110" s="196"/>
       <c r="B110" s="151" t="s">
         <v>491</v>
       </c>
@@ -39983,7 +40891,7 @@
       </c>
     </row>
     <row r="133" spans="1:9">
-      <c r="A133" s="218"/>
+      <c r="A133" s="216"/>
       <c r="B133" s="155" t="s">
         <v>456</v>
       </c>
@@ -40010,7 +40918,7 @@
       </c>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="218"/>
+      <c r="A134" s="216"/>
       <c r="B134" s="155" t="s">
         <v>456</v>
       </c>
@@ -40172,7 +41080,7 @@
       </c>
     </row>
     <row r="140" spans="1:9">
-      <c r="A140" s="198"/>
+      <c r="A140" s="196"/>
       <c r="B140" s="144" t="s">
         <v>471</v>
       </c>
@@ -40199,7 +41107,7 @@
       </c>
     </row>
     <row r="141" spans="1:9">
-      <c r="A141" s="198"/>
+      <c r="A141" s="196"/>
       <c r="B141" s="144" t="s">
         <v>471</v>
       </c>
@@ -40226,7 +41134,7 @@
       </c>
     </row>
     <row r="142" spans="1:9">
-      <c r="A142" s="198"/>
+      <c r="A142" s="196"/>
       <c r="B142" s="144" t="s">
         <v>471</v>
       </c>
@@ -40253,7 +41161,7 @@
       </c>
     </row>
     <row r="143" spans="1:9">
-      <c r="A143" s="198"/>
+      <c r="A143" s="196"/>
       <c r="B143" s="144" t="s">
         <v>471</v>
       </c>
@@ -40334,7 +41242,7 @@
       </c>
     </row>
     <row r="146" spans="1:10">
-      <c r="A146" s="218"/>
+      <c r="A146" s="216"/>
       <c r="B146" s="151" t="s">
         <v>518</v>
       </c>
@@ -40361,7 +41269,7 @@
       </c>
     </row>
     <row r="147" spans="1:10">
-      <c r="A147" s="202"/>
+      <c r="A147" s="200"/>
       <c r="B147" s="151" t="s">
         <v>518</v>
       </c>
@@ -40469,7 +41377,7 @@
       </c>
     </row>
     <row r="151" spans="1:10">
-      <c r="A151" s="216"/>
+      <c r="A151" s="217"/>
       <c r="B151" s="141" t="s">
         <v>582</v>
       </c>
@@ -40497,7 +41405,7 @@
       <c r="J151" s="59"/>
     </row>
     <row r="152" spans="1:10">
-      <c r="A152" s="217"/>
+      <c r="A152" s="218"/>
       <c r="B152" s="141" t="s">
         <v>582</v>
       </c>
@@ -40524,7 +41432,7 @@
       </c>
     </row>
     <row r="153" spans="1:10">
-      <c r="A153" s="198"/>
+      <c r="A153" s="196"/>
       <c r="B153" s="144" t="s">
         <v>526</v>
       </c>
@@ -40551,7 +41459,7 @@
       </c>
     </row>
     <row r="154" spans="1:10">
-      <c r="A154" s="198"/>
+      <c r="A154" s="196"/>
       <c r="B154" s="144" t="s">
         <v>526</v>
       </c>
@@ -40578,7 +41486,7 @@
       </c>
     </row>
     <row r="155" spans="1:10">
-      <c r="A155" s="198"/>
+      <c r="A155" s="196"/>
       <c r="B155" s="144" t="s">
         <v>526</v>
       </c>
@@ -40605,7 +41513,7 @@
       </c>
     </row>
     <row r="156" spans="1:10">
-      <c r="A156" s="198"/>
+      <c r="A156" s="196"/>
       <c r="B156" s="144" t="s">
         <v>526</v>
       </c>
@@ -40632,7 +41540,7 @@
       </c>
     </row>
     <row r="157" spans="1:10">
-      <c r="A157" s="198"/>
+      <c r="A157" s="196"/>
       <c r="B157" s="151" t="s">
         <v>590</v>
       </c>
@@ -40659,7 +41567,7 @@
       </c>
     </row>
     <row r="158" spans="1:10">
-      <c r="A158" s="198"/>
+      <c r="A158" s="196"/>
       <c r="B158" s="151" t="s">
         <v>590</v>
       </c>
@@ -40834,11 +41742,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="A133:A134"/>
-    <mergeCell ref="A140:A143"/>
-    <mergeCell ref="A146:A147"/>
     <mergeCell ref="A151:A152"/>
     <mergeCell ref="A153:A156"/>
     <mergeCell ref="A157:A158"/>
@@ -40851,6 +41754,11 @@
     <mergeCell ref="A85:A91"/>
     <mergeCell ref="A92:A94"/>
     <mergeCell ref="A103:A106"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="A133:A134"/>
+    <mergeCell ref="A140:A143"/>
+    <mergeCell ref="A146:A147"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -40882,17 +41790,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="194" t="s">
         <v>602</v>
       </c>
-      <c r="B1" s="197"/>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197"/>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="197"/>
+      <c r="B1" s="195"/>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="45" t="s">
@@ -40953,7 +41861,7 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="211"/>
+      <c r="A4" s="202"/>
       <c r="B4" s="151" t="s">
         <v>575</v>
       </c>
@@ -41009,7 +41917,7 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="201"/>
+      <c r="A6" s="199"/>
       <c r="B6" s="139" t="s">
         <v>584</v>
       </c>
@@ -41036,7 +41944,7 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="202"/>
+      <c r="A7" s="200"/>
       <c r="B7" s="139" t="s">
         <v>584</v>
       </c>
@@ -41092,7 +42000,7 @@
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="198"/>
+      <c r="A9" s="196"/>
       <c r="B9" s="151" t="s">
         <v>592</v>
       </c>
@@ -41148,7 +42056,7 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="198"/>
+      <c r="A11" s="196"/>
       <c r="B11" s="151" t="s">
         <v>618</v>
       </c>
@@ -42338,7 +43246,7 @@
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="218"/>
+      <c r="A55" s="216"/>
       <c r="B55" s="147" t="s">
         <v>615</v>
       </c>
@@ -42365,7 +43273,7 @@
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="218"/>
+      <c r="A56" s="216"/>
       <c r="B56" s="147" t="s">
         <v>615</v>
       </c>
@@ -42554,7 +43462,7 @@
       </c>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="201">
+      <c r="A63" s="199">
         <v>11</v>
       </c>
       <c r="B63" s="139" t="s">
@@ -42583,7 +43491,7 @@
       </c>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="218"/>
+      <c r="A64" s="216"/>
       <c r="B64" s="139" t="s">
         <v>631</v>
       </c>
@@ -42610,7 +43518,7 @@
       </c>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="218"/>
+      <c r="A65" s="216"/>
       <c r="B65" s="139" t="s">
         <v>631</v>
       </c>
@@ -42637,7 +43545,7 @@
       </c>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="218"/>
+      <c r="A66" s="216"/>
       <c r="B66" s="139" t="s">
         <v>631</v>
       </c>
@@ -42664,7 +43572,7 @@
       </c>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="218"/>
+      <c r="A67" s="216"/>
       <c r="B67" s="139" t="s">
         <v>631</v>
       </c>
@@ -42691,7 +43599,7 @@
       </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="218"/>
+      <c r="A68" s="216"/>
       <c r="B68" s="139" t="s">
         <v>631</v>
       </c>
@@ -43206,7 +44114,7 @@
       </c>
     </row>
     <row r="87" spans="1:9">
-      <c r="A87" s="198">
+      <c r="A87" s="196">
         <v>15</v>
       </c>
       <c r="B87" s="139" t="s">
@@ -43235,7 +44143,7 @@
       </c>
     </row>
     <row r="88" spans="1:9">
-      <c r="A88" s="198"/>
+      <c r="A88" s="196"/>
       <c r="B88" s="139" t="s">
         <v>626</v>
       </c>
@@ -43262,7 +44170,7 @@
       </c>
     </row>
     <row r="89" spans="1:9">
-      <c r="A89" s="198"/>
+      <c r="A89" s="196"/>
       <c r="B89" s="139" t="s">
         <v>626</v>
       </c>
@@ -43289,7 +44197,7 @@
       </c>
     </row>
     <row r="90" spans="1:9">
-      <c r="A90" s="198"/>
+      <c r="A90" s="196"/>
       <c r="B90" s="139" t="s">
         <v>626</v>
       </c>
@@ -43534,7 +44442,7 @@
       </c>
     </row>
     <row r="99" spans="1:9">
-      <c r="A99" s="201">
+      <c r="A99" s="199">
         <v>17</v>
       </c>
       <c r="B99" s="139" t="s">
@@ -43563,7 +44471,7 @@
       </c>
     </row>
     <row r="100" spans="1:9">
-      <c r="A100" s="218"/>
+      <c r="A100" s="216"/>
       <c r="B100" s="139" t="s">
         <v>549</v>
       </c>
@@ -43590,7 +44498,7 @@
       </c>
     </row>
     <row r="101" spans="1:9">
-      <c r="A101" s="218"/>
+      <c r="A101" s="216"/>
       <c r="B101" s="139" t="s">
         <v>549</v>
       </c>
@@ -43617,7 +44525,7 @@
       </c>
     </row>
     <row r="102" spans="1:9">
-      <c r="A102" s="218"/>
+      <c r="A102" s="216"/>
       <c r="B102" s="139" t="s">
         <v>549</v>
       </c>
@@ -43644,7 +44552,7 @@
       </c>
     </row>
     <row r="103" spans="1:9">
-      <c r="A103" s="218"/>
+      <c r="A103" s="216"/>
       <c r="B103" s="139" t="s">
         <v>549</v>
       </c>
@@ -43671,7 +44579,7 @@
       </c>
     </row>
     <row r="104" spans="1:9">
-      <c r="A104" s="218"/>
+      <c r="A104" s="216"/>
       <c r="B104" s="139" t="s">
         <v>549</v>
       </c>
@@ -43698,7 +44606,7 @@
       </c>
     </row>
     <row r="105" spans="1:9">
-      <c r="A105" s="202"/>
+      <c r="A105" s="200"/>
       <c r="B105" s="139" t="s">
         <v>549</v>
       </c>
@@ -44598,7 +45506,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="27.6">
+    <row r="138" spans="1:10">
       <c r="A138" s="50"/>
       <c r="B138" s="147" t="s">
         <v>765</v>
@@ -45481,17 +46389,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="197" t="s">
         <v>806</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="38" t="s">

--- a/contratos.xlsx
+++ b/contratos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Downloads\UFPI\projetoPortarias\site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9899D0AA-4CB4-4F45-81FC-EB5CABEE2175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2F35EC-E6ED-475C-B1F4-0BEAAE5EED65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2009" sheetId="5" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9823" uniqueCount="1703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9822" uniqueCount="1703">
   <si>
     <t>PLANILHA REFERENTE AOS CONTRATOS DE 2009</t>
   </si>
@@ -6205,27 +6205,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6247,16 +6226,37 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -33581,7 +33581,7 @@
       <c r="I10" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="J10" s="201" t="s">
+      <c r="J10" s="210" t="s">
         <v>194</v>
       </c>
     </row>
@@ -33613,7 +33613,7 @@
       <c r="I11" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="J11" s="201"/>
+      <c r="J11" s="210"/>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
       <c r="A12" s="18">
@@ -33643,7 +33643,7 @@
       <c r="I12" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="J12" s="201"/>
+      <c r="J12" s="210"/>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1">
       <c r="A13" s="17">
@@ -34483,10 +34483,10 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="48"/>
-      <c r="B43" s="210" t="s">
+      <c r="B43" s="203" t="s">
         <v>225</v>
       </c>
-      <c r="C43" s="213" t="s">
+      <c r="C43" s="206" t="s">
         <v>226</v>
       </c>
       <c r="D43" s="42" t="s">
@@ -34510,8 +34510,8 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="48"/>
-      <c r="B44" s="211"/>
-      <c r="C44" s="214"/>
+      <c r="B44" s="204"/>
+      <c r="C44" s="207"/>
       <c r="D44" s="42" t="s">
         <v>227</v>
       </c>
@@ -35149,10 +35149,10 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="48"/>
-      <c r="B67" s="211" t="s">
+      <c r="B67" s="204" t="s">
         <v>260</v>
       </c>
-      <c r="C67" s="204" t="s">
+      <c r="C67" s="208" t="s">
         <v>261</v>
       </c>
       <c r="D67" s="18" t="s">
@@ -35176,8 +35176,8 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="48"/>
-      <c r="B68" s="212"/>
-      <c r="C68" s="215"/>
+      <c r="B68" s="205"/>
+      <c r="C68" s="209"/>
       <c r="D68" s="28" t="s">
         <v>263</v>
       </c>
@@ -35225,7 +35225,7 @@
       </c>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" s="208">
+      <c r="A70" s="201">
         <v>29</v>
       </c>
       <c r="B70" s="149" t="s">
@@ -35254,7 +35254,7 @@
       </c>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="209"/>
+      <c r="A71" s="202"/>
       <c r="B71" s="149" t="s">
         <v>264</v>
       </c>
@@ -35283,7 +35283,7 @@
       <c r="K71" s="59"/>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="209"/>
+      <c r="A72" s="202"/>
       <c r="B72" s="149" t="s">
         <v>264</v>
       </c>
@@ -35312,7 +35312,7 @@
       <c r="K72" s="59"/>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="209"/>
+      <c r="A73" s="202"/>
       <c r="B73" s="149" t="s">
         <v>264</v>
       </c>
@@ -35514,10 +35514,10 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="50"/>
-      <c r="B80" s="205" t="s">
+      <c r="B80" s="213" t="s">
         <v>205</v>
       </c>
-      <c r="C80" s="202" t="s">
+      <c r="C80" s="211" t="s">
         <v>103</v>
       </c>
       <c r="D80" s="32" t="s">
@@ -35543,8 +35543,8 @@
       <c r="A81" s="50">
         <v>36</v>
       </c>
-      <c r="B81" s="205"/>
-      <c r="C81" s="202"/>
+      <c r="B81" s="213"/>
+      <c r="C81" s="211"/>
       <c r="D81" s="32" t="s">
         <v>276</v>
       </c>
@@ -35566,10 +35566,10 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="51"/>
-      <c r="B82" s="206" t="s">
+      <c r="B82" s="214" t="s">
         <v>277</v>
       </c>
-      <c r="C82" s="203" t="s">
+      <c r="C82" s="212" t="s">
         <v>278</v>
       </c>
       <c r="D82" s="32" t="s">
@@ -35595,8 +35595,8 @@
       <c r="A83" s="51">
         <v>37</v>
       </c>
-      <c r="B83" s="207"/>
-      <c r="C83" s="204"/>
+      <c r="B83" s="215"/>
+      <c r="C83" s="208"/>
       <c r="D83" s="42" t="s">
         <v>279</v>
       </c>
@@ -37281,17 +37281,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="J10:J12"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="B82:B83"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A70:A73"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="B67:B68"/>
     <mergeCell ref="C43:C44"/>
     <mergeCell ref="C67:C68"/>
-    <mergeCell ref="J10:J12"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B82:B83"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -38686,7 +38686,7 @@
       <c r="I51" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="J51" s="201" t="s">
+      <c r="J51" s="210" t="s">
         <v>452</v>
       </c>
     </row>
@@ -38716,7 +38716,7 @@
       <c r="I52" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="J52" s="201"/>
+      <c r="J52" s="210"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="51"/>
@@ -40096,7 +40096,7 @@
       </c>
     </row>
     <row r="104" spans="1:21">
-      <c r="A104" s="216"/>
+      <c r="A104" s="218"/>
       <c r="B104" s="139" t="s">
         <v>490</v>
       </c>
@@ -40123,7 +40123,7 @@
       </c>
     </row>
     <row r="105" spans="1:21">
-      <c r="A105" s="216"/>
+      <c r="A105" s="218"/>
       <c r="B105" s="139" t="s">
         <v>490</v>
       </c>
@@ -40150,7 +40150,7 @@
       </c>
     </row>
     <row r="106" spans="1:21">
-      <c r="A106" s="216"/>
+      <c r="A106" s="218"/>
       <c r="B106" s="139" t="s">
         <v>490</v>
       </c>
@@ -40891,7 +40891,7 @@
       </c>
     </row>
     <row r="133" spans="1:9">
-      <c r="A133" s="216"/>
+      <c r="A133" s="218"/>
       <c r="B133" s="155" t="s">
         <v>456</v>
       </c>
@@ -40918,7 +40918,7 @@
       </c>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="216"/>
+      <c r="A134" s="218"/>
       <c r="B134" s="155" t="s">
         <v>456</v>
       </c>
@@ -41242,7 +41242,7 @@
       </c>
     </row>
     <row r="146" spans="1:10">
-      <c r="A146" s="216"/>
+      <c r="A146" s="218"/>
       <c r="B146" s="151" t="s">
         <v>518</v>
       </c>
@@ -41377,7 +41377,7 @@
       </c>
     </row>
     <row r="151" spans="1:10">
-      <c r="A151" s="217"/>
+      <c r="A151" s="216"/>
       <c r="B151" s="141" t="s">
         <v>582</v>
       </c>
@@ -41405,7 +41405,7 @@
       <c r="J151" s="59"/>
     </row>
     <row r="152" spans="1:10">
-      <c r="A152" s="218"/>
+      <c r="A152" s="217"/>
       <c r="B152" s="141" t="s">
         <v>582</v>
       </c>
@@ -41742,6 +41742,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="A133:A134"/>
+    <mergeCell ref="A140:A143"/>
+    <mergeCell ref="A146:A147"/>
     <mergeCell ref="A151:A152"/>
     <mergeCell ref="A153:A156"/>
     <mergeCell ref="A157:A158"/>
@@ -41754,11 +41759,6 @@
     <mergeCell ref="A85:A91"/>
     <mergeCell ref="A92:A94"/>
     <mergeCell ref="A103:A106"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="A133:A134"/>
-    <mergeCell ref="A140:A143"/>
-    <mergeCell ref="A146:A147"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -41861,7 +41861,7 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="202"/>
+      <c r="A4" s="211"/>
       <c r="B4" s="151" t="s">
         <v>575</v>
       </c>
@@ -43246,7 +43246,7 @@
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="216"/>
+      <c r="A55" s="218"/>
       <c r="B55" s="147" t="s">
         <v>615</v>
       </c>
@@ -43273,7 +43273,7 @@
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="216"/>
+      <c r="A56" s="218"/>
       <c r="B56" s="147" t="s">
         <v>615</v>
       </c>
@@ -43491,7 +43491,7 @@
       </c>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="216"/>
+      <c r="A64" s="218"/>
       <c r="B64" s="139" t="s">
         <v>631</v>
       </c>
@@ -43518,7 +43518,7 @@
       </c>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="216"/>
+      <c r="A65" s="218"/>
       <c r="B65" s="139" t="s">
         <v>631</v>
       </c>
@@ -43545,7 +43545,7 @@
       </c>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="216"/>
+      <c r="A66" s="218"/>
       <c r="B66" s="139" t="s">
         <v>631</v>
       </c>
@@ -43572,7 +43572,7 @@
       </c>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="216"/>
+      <c r="A67" s="218"/>
       <c r="B67" s="139" t="s">
         <v>631</v>
       </c>
@@ -43599,7 +43599,7 @@
       </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="216"/>
+      <c r="A68" s="218"/>
       <c r="B68" s="139" t="s">
         <v>631</v>
       </c>
@@ -44471,7 +44471,7 @@
       </c>
     </row>
     <row r="100" spans="1:9">
-      <c r="A100" s="216"/>
+      <c r="A100" s="218"/>
       <c r="B100" s="139" t="s">
         <v>549</v>
       </c>
@@ -44498,7 +44498,7 @@
       </c>
     </row>
     <row r="101" spans="1:9">
-      <c r="A101" s="216"/>
+      <c r="A101" s="218"/>
       <c r="B101" s="139" t="s">
         <v>549</v>
       </c>
@@ -44525,7 +44525,7 @@
       </c>
     </row>
     <row r="102" spans="1:9">
-      <c r="A102" s="216"/>
+      <c r="A102" s="218"/>
       <c r="B102" s="139" t="s">
         <v>549</v>
       </c>
@@ -44552,7 +44552,7 @@
       </c>
     </row>
     <row r="103" spans="1:9">
-      <c r="A103" s="216"/>
+      <c r="A103" s="218"/>
       <c r="B103" s="139" t="s">
         <v>549</v>
       </c>
@@ -44579,7 +44579,7 @@
       </c>
     </row>
     <row r="104" spans="1:9">
-      <c r="A104" s="216"/>
+      <c r="A104" s="218"/>
       <c r="B104" s="139" t="s">
         <v>549</v>
       </c>
@@ -45506,7 +45506,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" ht="27.6">
       <c r="A138" s="50"/>
       <c r="B138" s="147" t="s">
         <v>765</v>

--- a/contratos.xlsx
+++ b/contratos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Downloads\UFPI\projetoPortarias\site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2F35EC-E6ED-475C-B1F4-0BEAAE5EED65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB68ADF-1D63-49BA-A0E0-E2CF4093162D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2009" sheetId="5" r:id="rId1"/>
@@ -6166,13 +6166,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6274,13 +6274,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7234,17 +7234,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="224" t="s">
         <v>957</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="189"/>
-      <c r="F1" s="189"/>
-      <c r="G1" s="189"/>
-      <c r="H1" s="189"/>
-      <c r="I1" s="189"/>
+      <c r="B1" s="225"/>
+      <c r="C1" s="225"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="225"/>
+      <c r="F1" s="225"/>
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -14465,7 +14465,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="7.88671875" style="1" customWidth="1"/>
@@ -14480,17 +14480,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="224" t="s">
+      <c r="A1" s="188" t="s">
         <v>1154</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="23" t="s">
@@ -16453,6 +16453,16 @@
       <c r="I74" s="16" t="s">
         <v>182</v>
       </c>
+    </row>
+    <row r="75" spans="2:9">
+      <c r="B75" s="154"/>
+      <c r="C75" s="154"/>
+      <c r="D75" s="167"/>
+      <c r="E75" s="46"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="16"/>
+      <c r="I75" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16482,17 +16492,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="224" t="s">
         <v>1229</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="189"/>
-      <c r="F1" s="189"/>
-      <c r="G1" s="189"/>
-      <c r="H1" s="189"/>
-      <c r="I1" s="189"/>
+      <c r="B1" s="225"/>
+      <c r="C1" s="225"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="225"/>
+      <c r="F1" s="225"/>
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -23564,17 +23574,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="224" t="s">
+      <c r="A1" s="188" t="s">
         <v>1393</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="19" t="s">
@@ -27151,17 +27161,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="224" t="s">
         <v>1504</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="189"/>
-      <c r="F1" s="189"/>
-      <c r="G1" s="189"/>
-      <c r="H1" s="189"/>
-      <c r="I1" s="189"/>
+      <c r="B1" s="225"/>
+      <c r="C1" s="225"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="225"/>
+      <c r="F1" s="225"/>
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -48119,17 +48129,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A1" s="224" t="s">
+      <c r="A1" s="188" t="s">
         <v>1685</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="38" t="s">
@@ -48306,17 +48316,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27" customHeight="1">
-      <c r="A1" s="224" t="s">
+      <c r="A1" s="188" t="s">
         <v>883</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="23" t="s">

--- a/contratos.xlsx
+++ b/contratos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Downloads\UFPI\projetoPortarias\site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB68ADF-1D63-49BA-A0E0-E2CF4093162D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2FF487-3FA4-4BEF-A37D-0BC93768BA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2009" sheetId="5" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9822" uniqueCount="1703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9822" uniqueCount="1680">
   <si>
     <t>PLANILHA REFERENTE AOS CONTRATOS DE 2009</t>
   </si>
@@ -5029,45 +5029,24 @@
     <t>05/2021</t>
   </si>
   <si>
-    <t>31/2021</t>
-  </si>
-  <si>
     <t>05/2022</t>
   </si>
   <si>
-    <t>31/2022</t>
-  </si>
-  <si>
     <t>05/2023</t>
   </si>
   <si>
-    <t>31/2023</t>
-  </si>
-  <si>
     <t>05/2024</t>
   </si>
   <si>
-    <t>31/2024</t>
-  </si>
-  <si>
     <t>05/2025</t>
   </si>
   <si>
-    <t>31/2025</t>
-  </si>
-  <si>
     <t>05/2026</t>
   </si>
   <si>
-    <t>31/2026</t>
-  </si>
-  <si>
     <t>05/2027</t>
   </si>
   <si>
-    <t>31/2027</t>
-  </si>
-  <si>
     <t>05/2028</t>
   </si>
   <si>
@@ -5110,39 +5089,12 @@
     <t>05/2041</t>
   </si>
   <si>
-    <t>86/2021</t>
-  </si>
-  <si>
-    <t>86/2022</t>
-  </si>
-  <si>
-    <t>86/2023</t>
-  </si>
-  <si>
-    <t>86/2024</t>
-  </si>
-  <si>
-    <t>86/2025</t>
-  </si>
-  <si>
-    <t>86/2026</t>
-  </si>
-  <si>
-    <t>86/2027</t>
-  </si>
-  <si>
-    <t>86/2028</t>
-  </si>
-  <si>
     <t>06/2017</t>
   </si>
   <si>
     <t>08/2017</t>
   </si>
   <si>
-    <t>98/2020</t>
-  </si>
-  <si>
     <t>PLANILHA SEM NUMERO DE CONTRATO</t>
   </si>
   <si>
@@ -5174,27 +5126,6 @@
   </si>
   <si>
     <t>09/2024</t>
-  </si>
-  <si>
-    <t>121/2018</t>
-  </si>
-  <si>
-    <t>79/2017</t>
-  </si>
-  <si>
-    <t>39/2018</t>
-  </si>
-  <si>
-    <t>37/2018</t>
-  </si>
-  <si>
-    <t>37/2019</t>
-  </si>
-  <si>
-    <t>131/2021</t>
-  </si>
-  <si>
-    <t>131/2022</t>
   </si>
 </sst>
 </file>
@@ -5601,7 +5532,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6283,6 +6214,9 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8657,8 +8591,8 @@
       <c r="C55" s="136" t="s">
         <v>985</v>
       </c>
-      <c r="D55" s="147" t="s">
-        <v>1008</v>
+      <c r="D55" s="227" t="s">
+        <v>1208</v>
       </c>
       <c r="E55" s="145">
         <v>43136</v>
@@ -8684,8 +8618,8 @@
       <c r="C56" s="136" t="s">
         <v>985</v>
       </c>
-      <c r="D56" s="147" t="s">
-        <v>1008</v>
+      <c r="D56" s="227" t="s">
+        <v>1208</v>
       </c>
       <c r="E56" s="145">
         <v>43136</v>
@@ -8711,8 +8645,8 @@
       <c r="C57" s="136" t="s">
         <v>985</v>
       </c>
-      <c r="D57" s="147" t="s">
-        <v>1008</v>
+      <c r="D57" s="227" t="s">
+        <v>1208</v>
       </c>
       <c r="E57" s="145">
         <v>43136</v>
@@ -16477,7 +16411,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I263"/>
+  <dimension ref="A1:I264"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="7.88671875" style="1" customWidth="1"/>
@@ -23545,6 +23479,16 @@
       <c r="I263" s="16" t="s">
         <v>15</v>
       </c>
+    </row>
+    <row r="264" spans="2:9">
+      <c r="B264" s="147"/>
+      <c r="C264" s="136"/>
+      <c r="D264" s="147"/>
+      <c r="E264" s="145"/>
+      <c r="F264" s="16"/>
+      <c r="G264" s="16"/>
+      <c r="H264" s="16"/>
+      <c r="I264" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -24698,7 +24642,7 @@
     <row r="43" spans="1:9" ht="15" customHeight="1">
       <c r="A43" s="20"/>
       <c r="B43" s="135" t="s">
-        <v>1686</v>
+        <v>1670</v>
       </c>
       <c r="C43" s="135" t="s">
         <v>639</v>
@@ -24725,7 +24669,7 @@
     <row r="44" spans="1:9" ht="15" customHeight="1">
       <c r="A44" s="20"/>
       <c r="B44" s="135" t="s">
-        <v>1687</v>
+        <v>1671</v>
       </c>
       <c r="C44" s="135" t="s">
         <v>639</v>
@@ -24752,7 +24696,7 @@
     <row r="45" spans="1:9" ht="15" customHeight="1">
       <c r="A45" s="20"/>
       <c r="B45" s="135" t="s">
-        <v>1688</v>
+        <v>1672</v>
       </c>
       <c r="C45" s="135" t="s">
         <v>639</v>
@@ -24779,7 +24723,7 @@
     <row r="46" spans="1:9" ht="15" customHeight="1">
       <c r="A46" s="20"/>
       <c r="B46" s="135" t="s">
-        <v>1689</v>
+        <v>1673</v>
       </c>
       <c r="C46" s="135" t="s">
         <v>639</v>
@@ -24806,7 +24750,7 @@
     <row r="47" spans="1:9" ht="15" customHeight="1">
       <c r="A47" s="20"/>
       <c r="B47" s="135" t="s">
-        <v>1690</v>
+        <v>1674</v>
       </c>
       <c r="C47" s="135" t="s">
         <v>639</v>
@@ -27130,7 +27074,16 @@
         <v>182</v>
       </c>
     </row>
-    <row r="134" spans="2:9" ht="13.8" customHeight="1"/>
+    <row r="134" spans="2:9" ht="13.8" customHeight="1">
+      <c r="B134" s="135"/>
+      <c r="C134" s="135"/>
+      <c r="D134" s="135"/>
+      <c r="E134" s="137"/>
+      <c r="F134" s="16"/>
+      <c r="G134" s="16"/>
+      <c r="H134" s="16"/>
+      <c r="I134" s="16"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
@@ -48130,7 +48083,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16.2" thickBot="1">
       <c r="A1" s="188" t="s">
-        <v>1685</v>
+        <v>1669</v>
       </c>
       <c r="B1" s="189"/>
       <c r="C1" s="189"/>
@@ -48393,10 +48346,10 @@
         <v>884</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1063</v>
+        <v>885</v>
       </c>
       <c r="E4" s="7">
-        <v>42434</v>
+        <v>42433</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>110</v>
@@ -48420,10 +48373,10 @@
         <v>884</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1144</v>
+        <v>885</v>
       </c>
       <c r="E5" s="7">
-        <v>42435</v>
+        <v>42433</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>13</v>
@@ -48447,10 +48400,10 @@
         <v>884</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1283</v>
+        <v>885</v>
       </c>
       <c r="E6" s="7">
-        <v>42436</v>
+        <v>42433</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>110</v>
@@ -48474,10 +48427,10 @@
         <v>884</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1466</v>
+        <v>885</v>
       </c>
       <c r="E7" s="7">
-        <v>42437</v>
+        <v>42433</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>13</v>
@@ -48501,10 +48454,10 @@
         <v>884</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1647</v>
+        <v>885</v>
       </c>
       <c r="E8" s="7">
-        <v>42438</v>
+        <v>42433</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>110</v>
@@ -48522,16 +48475,16 @@
     <row r="9" spans="1:9" ht="15" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" s="9" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1649</v>
+        <v>885</v>
       </c>
       <c r="E9" s="7">
-        <v>42439</v>
+        <v>42433</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>13</v>
@@ -48549,16 +48502,16 @@
     <row r="10" spans="1:9" ht="15" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" s="9" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1651</v>
+        <v>885</v>
       </c>
       <c r="E10" s="7">
-        <v>42440</v>
+        <v>42433</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>110</v>
@@ -48576,16 +48529,16 @@
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="8"/>
       <c r="B11" s="9" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1653</v>
+        <v>885</v>
       </c>
       <c r="E11" s="7">
-        <v>42441</v>
+        <v>42433</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>13</v>
@@ -48603,16 +48556,16 @@
     <row r="12" spans="1:9" ht="15" customHeight="1">
       <c r="A12" s="8"/>
       <c r="B12" s="9" t="s">
-        <v>1654</v>
+        <v>1650</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1655</v>
+        <v>885</v>
       </c>
       <c r="E12" s="7">
-        <v>42442</v>
+        <v>42433</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>110</v>
@@ -48630,16 +48583,16 @@
     <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="8"/>
       <c r="B13" s="9" t="s">
-        <v>1656</v>
+        <v>1651</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1657</v>
+        <v>885</v>
       </c>
       <c r="E13" s="7">
-        <v>42443</v>
+        <v>42433</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>13</v>
@@ -48657,16 +48610,16 @@
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="8"/>
       <c r="B14" s="9" t="s">
-        <v>1658</v>
+        <v>1652</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1659</v>
+        <v>885</v>
       </c>
       <c r="E14" s="7">
-        <v>42444</v>
+        <v>42433</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>110</v>
@@ -48684,7 +48637,7 @@
     <row r="15" spans="1:9" ht="15" customHeight="1">
       <c r="A15" s="8"/>
       <c r="B15" s="9" t="s">
-        <v>1660</v>
+        <v>1653</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>884</v>
@@ -48711,16 +48664,16 @@
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="8"/>
       <c r="B16" s="9" t="s">
-        <v>1661</v>
+        <v>1654</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>364</v>
+        <v>890</v>
       </c>
       <c r="E16" s="10">
-        <v>42791</v>
+        <v>42790</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>110</v>
@@ -48738,7 +48691,7 @@
     <row r="17" spans="1:10" ht="15" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="9" t="s">
-        <v>1662</v>
+        <v>1655</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>884</v>
@@ -48765,16 +48718,16 @@
     <row r="18" spans="1:10" ht="15" customHeight="1">
       <c r="A18" s="8"/>
       <c r="B18" s="9" t="s">
-        <v>1663</v>
+        <v>1656</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1507</v>
+        <v>891</v>
       </c>
       <c r="E18" s="7">
-        <v>42832</v>
+        <v>42831</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>110</v>
@@ -48792,16 +48745,16 @@
     <row r="19" spans="1:10" ht="15" customHeight="1">
       <c r="A19" s="8"/>
       <c r="B19" s="9" t="s">
-        <v>1664</v>
+        <v>1657</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1311</v>
+        <v>891</v>
       </c>
       <c r="E19" s="7">
-        <v>42833</v>
+        <v>42831</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>13</v>
@@ -48819,16 +48772,16 @@
     <row r="20" spans="1:10" ht="15" customHeight="1">
       <c r="A20" s="8"/>
       <c r="B20" s="9" t="s">
-        <v>1665</v>
+        <v>1658</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1095</v>
+        <v>891</v>
       </c>
       <c r="E20" s="7">
-        <v>42834</v>
+        <v>42831</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>110</v>
@@ -48846,16 +48799,16 @@
     <row r="21" spans="1:10" ht="15" customHeight="1">
       <c r="A21" s="8"/>
       <c r="B21" s="9" t="s">
-        <v>1666</v>
+        <v>1659</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1674</v>
+        <v>891</v>
       </c>
       <c r="E21" s="7">
-        <v>42835</v>
+        <v>42831</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>13</v>
@@ -48873,16 +48826,16 @@
     <row r="22" spans="1:10" ht="15" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="9" t="s">
-        <v>1667</v>
+        <v>1660</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1675</v>
+        <v>891</v>
       </c>
       <c r="E22" s="7">
-        <v>42836</v>
+        <v>42831</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>110</v>
@@ -48900,16 +48853,16 @@
     <row r="23" spans="1:10" ht="15" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="9" t="s">
-        <v>1668</v>
+        <v>1661</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1676</v>
+        <v>891</v>
       </c>
       <c r="E23" s="7">
-        <v>42837</v>
+        <v>42831</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>13</v>
@@ -48927,16 +48880,16 @@
     <row r="24" spans="1:10" ht="15" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="9" t="s">
-        <v>1669</v>
+        <v>1662</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1677</v>
+        <v>891</v>
       </c>
       <c r="E24" s="7">
-        <v>42838</v>
+        <v>42831</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>110</v>
@@ -48954,16 +48907,16 @@
     <row r="25" spans="1:10" ht="15" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="9" t="s">
-        <v>1670</v>
+        <v>1663</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1678</v>
+        <v>891</v>
       </c>
       <c r="E25" s="7">
-        <v>42839</v>
+        <v>42831</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>13</v>
@@ -48981,16 +48934,16 @@
     <row r="26" spans="1:10" ht="15" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="9" t="s">
-        <v>1671</v>
+        <v>1664</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1679</v>
+        <v>891</v>
       </c>
       <c r="E26" s="7">
-        <v>42840</v>
+        <v>42831</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>110</v>
@@ -49008,16 +48961,16 @@
     <row r="27" spans="1:10" ht="15" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="9" t="s">
-        <v>1672</v>
+        <v>1665</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1680</v>
+        <v>891</v>
       </c>
       <c r="E27" s="7">
-        <v>42841</v>
+        <v>42831</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>13</v>
@@ -49035,16 +48988,16 @@
     <row r="28" spans="1:10" ht="15" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="9" t="s">
-        <v>1673</v>
+        <v>1666</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>884</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1681</v>
+        <v>891</v>
       </c>
       <c r="E28" s="7">
-        <v>42842</v>
+        <v>42831</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>110</v>
@@ -49089,16 +49042,16 @@
     <row r="30" spans="1:10" ht="15" customHeight="1">
       <c r="A30" s="8"/>
       <c r="B30" s="9" t="s">
-        <v>1682</v>
+        <v>1667</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>893</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>23</v>
+        <v>894</v>
       </c>
       <c r="E30" s="10">
-        <v>42501</v>
+        <v>42500</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>13</v>
@@ -49138,7 +49091,7 @@
     <row r="32" spans="1:10" ht="15" customHeight="1">
       <c r="A32" s="8"/>
       <c r="B32" s="6" t="s">
-        <v>1683</v>
+        <v>1668</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>897</v>
@@ -49171,10 +49124,10 @@
         <v>897</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>1326</v>
+        <v>900</v>
       </c>
       <c r="E33" s="10">
-        <v>43277</v>
+        <v>43276</v>
       </c>
       <c r="F33" s="16" t="s">
         <v>13</v>
@@ -49198,10 +49151,10 @@
         <v>897</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>1684</v>
+        <v>900</v>
       </c>
       <c r="E34" s="10">
-        <v>43278</v>
+        <v>43276</v>
       </c>
       <c r="F34" s="16" t="s">
         <v>110</v>
@@ -49241,7 +49194,7 @@
     <row r="36" spans="1:10" ht="15" customHeight="1">
       <c r="A36" s="8"/>
       <c r="B36" s="167" t="s">
-        <v>1691</v>
+        <v>1675</v>
       </c>
       <c r="C36" s="154" t="s">
         <v>903</v>
@@ -49349,7 +49302,7 @@
     <row r="40" spans="1:10" ht="15" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="167" t="s">
-        <v>1692</v>
+        <v>1676</v>
       </c>
       <c r="C40" s="154" t="s">
         <v>903</v>
@@ -49376,7 +49329,7 @@
     <row r="41" spans="1:10" ht="15" customHeight="1">
       <c r="A41" s="16"/>
       <c r="B41" s="167" t="s">
-        <v>1693</v>
+        <v>1677</v>
       </c>
       <c r="C41" s="154" t="s">
         <v>903</v>
@@ -49403,7 +49356,7 @@
     <row r="42" spans="1:10" ht="15" customHeight="1">
       <c r="A42" s="16"/>
       <c r="B42" s="167" t="s">
-        <v>1694</v>
+        <v>1678</v>
       </c>
       <c r="C42" s="154" t="s">
         <v>903</v>
@@ -49430,7 +49383,7 @@
     <row r="43" spans="1:10" ht="15" customHeight="1">
       <c r="A43" s="16"/>
       <c r="B43" s="167" t="s">
-        <v>1695</v>
+        <v>1679</v>
       </c>
       <c r="C43" s="154" t="s">
         <v>903</v>
@@ -49652,10 +49605,10 @@
         <v>917</v>
       </c>
       <c r="D51" s="172" t="s">
-        <v>670</v>
+        <v>918</v>
       </c>
       <c r="E51" s="171">
-        <v>42600</v>
+        <v>42599</v>
       </c>
       <c r="F51" s="16" t="s">
         <v>110</v>
@@ -49706,10 +49659,10 @@
         <v>920</v>
       </c>
       <c r="D53" s="172" t="s">
-        <v>286</v>
+        <v>921</v>
       </c>
       <c r="E53" s="171">
-        <v>42592</v>
+        <v>42591</v>
       </c>
       <c r="F53" s="16" t="s">
         <v>110</v>
@@ -49787,10 +49740,10 @@
         <v>924</v>
       </c>
       <c r="D56" s="167" t="s">
-        <v>1696</v>
+        <v>926</v>
       </c>
       <c r="E56" s="46">
-        <v>42973</v>
+        <v>42972</v>
       </c>
       <c r="F56" s="32" t="s">
         <v>110</v>
@@ -50192,10 +50145,10 @@
         <v>942</v>
       </c>
       <c r="D71" s="167" t="s">
-        <v>1697</v>
+        <v>943</v>
       </c>
       <c r="E71" s="46">
-        <v>42691</v>
+        <v>42690</v>
       </c>
       <c r="F71" s="16" t="s">
         <v>110</v>
@@ -50262,10 +50215,10 @@
         <v>946</v>
       </c>
       <c r="D74" s="167" t="s">
-        <v>1697</v>
+        <v>943</v>
       </c>
       <c r="E74" s="46">
-        <v>42691</v>
+        <v>42690</v>
       </c>
       <c r="F74" s="16" t="s">
         <v>110</v>
@@ -50316,10 +50269,10 @@
         <v>947</v>
       </c>
       <c r="D76" s="172" t="s">
-        <v>1698</v>
+        <v>108</v>
       </c>
       <c r="E76" s="46">
-        <v>42769</v>
+        <v>42768</v>
       </c>
       <c r="F76" s="16" t="s">
         <v>13</v>
@@ -50343,10 +50296,10 @@
         <v>947</v>
       </c>
       <c r="D77" s="172" t="s">
-        <v>1316</v>
+        <v>108</v>
       </c>
       <c r="E77" s="46">
-        <v>42770</v>
+        <v>42768</v>
       </c>
       <c r="F77" s="16" t="s">
         <v>110</v>
@@ -50397,10 +50350,10 @@
         <v>950</v>
       </c>
       <c r="D79" s="167" t="s">
-        <v>1699</v>
+        <v>951</v>
       </c>
       <c r="E79" s="46">
-        <v>42769</v>
+        <v>42768</v>
       </c>
       <c r="F79" s="16" t="s">
         <v>13</v>
@@ -50424,10 +50377,10 @@
         <v>950</v>
       </c>
       <c r="D80" s="167" t="s">
-        <v>1700</v>
+        <v>951</v>
       </c>
       <c r="E80" s="46">
-        <v>42770</v>
+        <v>42768</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>110</v>
@@ -50478,10 +50431,10 @@
         <v>950</v>
       </c>
       <c r="D82" s="167" t="s">
-        <v>1701</v>
+        <v>955</v>
       </c>
       <c r="E82" s="46">
-        <v>44159</v>
+        <v>44158</v>
       </c>
       <c r="F82" s="16" t="s">
         <v>13</v>
@@ -50505,10 +50458,10 @@
         <v>950</v>
       </c>
       <c r="D83" s="167" t="s">
-        <v>1702</v>
+        <v>955</v>
       </c>
       <c r="E83" s="46">
-        <v>44160</v>
+        <v>44158</v>
       </c>
       <c r="F83" s="16" t="s">
         <v>110</v>
@@ -50525,14 +50478,14 @@
     </row>
     <row r="84" spans="1:9" ht="15" customHeight="1">
       <c r="A84"/>
-      <c r="B84"/>
-      <c r="C84"/>
-      <c r="D84"/>
-      <c r="E84"/>
-      <c r="F84"/>
-      <c r="G84"/>
-      <c r="H84"/>
-      <c r="I84"/>
+      <c r="B84" s="167"/>
+      <c r="C84" s="152"/>
+      <c r="D84" s="172"/>
+      <c r="E84" s="171"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="16"/>
+      <c r="H84" s="16"/>
+      <c r="I84" s="16"/>
     </row>
     <row r="85" spans="1:9" ht="15" customHeight="1">
       <c r="A85"/>
@@ -50606,5 +50559,6 @@
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>